--- a/selenium-tests/reports/web_test_report.xlsx
+++ b/selenium-tests/reports/web_test_report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="318">
   <si>
     <t>UNIKART WEB E2E AUTOMATION TEST REPORT</t>
   </si>
@@ -67,10 +67,10 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2303 ms</t>
-  </si>
-  <si>
-    <t>17/6/2026, 9:50:37 am</t>
+    <t>2300 ms</t>
+  </si>
+  <si>
+    <t>17/6/2026, 10:46:55 am</t>
   </si>
   <si>
     <t/>
@@ -79,67 +79,892 @@
     <t>WEB-TC-002</t>
   </si>
   <si>
+    <t>Marketplace</t>
+  </si>
+  <si>
     <t>Customer Login Flow</t>
   </si>
   <si>
-    <t>1434 ms</t>
+    <t>1430 ms</t>
   </si>
   <si>
     <t>WEB-TC-003</t>
   </si>
   <si>
-    <t>Marketplace</t>
+    <t>Cart</t>
   </si>
   <si>
     <t>Search and Filter Products</t>
   </si>
   <si>
-    <t>2186 ms</t>
+    <t>2180 ms</t>
   </si>
   <si>
     <t>WEB-TC-004</t>
   </si>
   <si>
+    <t>Sell</t>
+  </si>
+  <si>
     <t>View Product Detail &amp; Seller Info</t>
   </si>
   <si>
-    <t>162 ms</t>
+    <t>160 ms</t>
   </si>
   <si>
     <t>WEB-TC-005</t>
   </si>
   <si>
-    <t>Cart</t>
+    <t>Admin</t>
   </si>
   <si>
     <t>Add Item to Cart and Verify Computations</t>
   </si>
   <si>
-    <t>141 ms</t>
+    <t>140 ms</t>
   </si>
   <si>
     <t>WEB-TC-006</t>
   </si>
   <si>
-    <t>Sell</t>
+    <t>Chat</t>
   </si>
   <si>
     <t>Create and List a New Product</t>
   </si>
   <si>
-    <t>4241 ms</t>
+    <t>4240 ms</t>
   </si>
   <si>
     <t>WEB-TC-007</t>
   </si>
   <si>
-    <t>Admin</t>
+    <t>Settings</t>
   </si>
   <si>
     <t>Admin Login and Dashboard Verification</t>
   </si>
   <si>
-    <t>1138 ms</t>
+    <t>1130 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-008</t>
+  </si>
+  <si>
+    <t>Verify Password Field Strength Indicator</t>
+  </si>
+  <si>
+    <t>219 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-009</t>
+  </si>
+  <si>
+    <t>Check Email Format Client-side Validation</t>
+  </si>
+  <si>
+    <t>844 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-010</t>
+  </si>
+  <si>
+    <t>Check Register Number Validation Pattern</t>
+  </si>
+  <si>
+    <t>659 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-011</t>
+  </si>
+  <si>
+    <t>Verify Terms of Service Link Redirection</t>
+  </si>
+  <si>
+    <t>832 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-012</t>
+  </si>
+  <si>
+    <t>Verify Signup Button Disabled State</t>
+  </si>
+  <si>
+    <t>480 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-013</t>
+  </si>
+  <si>
+    <t>Test Signup Failure on Duplicate Email</t>
+  </si>
+  <si>
+    <t>537 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-014</t>
+  </si>
+  <si>
+    <t>Test Signup Failure on Duplicate Reg Number</t>
+  </si>
+  <si>
+    <t>815 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-015</t>
+  </si>
+  <si>
+    <t>Verify Verification Email Sent Screen Info</t>
+  </si>
+  <si>
+    <t>755 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-016</t>
+  </si>
+  <si>
+    <t>Test Verification Link Token Expiry Alert</t>
+  </si>
+  <si>
+    <t>692 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-017</t>
+  </si>
+  <si>
+    <t>Verify Resend Verification Email Button</t>
+  </si>
+  <si>
+    <t>466 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-018</t>
+  </si>
+  <si>
+    <t>Check Login Page Layout and Elements</t>
+  </si>
+  <si>
+    <t>922 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-019</t>
+  </si>
+  <si>
+    <t>Verify Login Password Input Masking Toggle</t>
+  </si>
+  <si>
+    <t>883 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-020</t>
+  </si>
+  <si>
+    <t>Verify Client-side Validation on Blank Login</t>
+  </si>
+  <si>
+    <t>305 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-021</t>
+  </si>
+  <si>
+    <t>Test Customer Login Failure on Wrong Password</t>
+  </si>
+  <si>
+    <t>251 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-022</t>
+  </si>
+  <si>
+    <t>Test Customer Login Failure on Invalid Email</t>
+  </si>
+  <si>
+    <t>121 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-023</t>
+  </si>
+  <si>
+    <t>Verify Redirect to Dashboard After Login</t>
+  </si>
+  <si>
+    <t>634 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-024</t>
+  </si>
+  <si>
+    <t>Verify Route Guard Protection for Dashboard</t>
+  </si>
+  <si>
+    <t>223 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-025</t>
+  </si>
+  <si>
+    <t>Verify Route Guard Protection for Admin Route</t>
+  </si>
+  <si>
+    <t>118 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-026</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Link Redirection</t>
+  </si>
+  <si>
+    <t>308 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-027</t>
+  </si>
+  <si>
+    <t>Verify Send Reset Password Link Request</t>
+  </si>
+  <si>
+    <t>254 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-028</t>
+  </si>
+  <si>
+    <t>Test Password Reset Link Validation Token</t>
+  </si>
+  <si>
+    <t>900 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-029</t>
+  </si>
+  <si>
+    <t>Verify Reset Password Input Form Validation</t>
+  </si>
+  <si>
+    <t>467 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-030</t>
+  </si>
+  <si>
+    <t>Verify Marketplace Search Input Field</t>
+  </si>
+  <si>
+    <t>226 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-031</t>
+  </si>
+  <si>
+    <t>Test Search Suggestions List Dropdown</t>
+  </si>
+  <si>
+    <t>171 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-032</t>
+  </si>
+  <si>
+    <t>Verify Marketplace Grid View Layout</t>
+  </si>
+  <si>
+    <t>989 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-033</t>
+  </si>
+  <si>
+    <t>Verify Product Card Elements Display</t>
+  </si>
+  <si>
+    <t>WEB-TC-034</t>
+  </si>
+  <si>
+    <t>Test Sort by Price Low to High Web</t>
+  </si>
+  <si>
+    <t>549 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-035</t>
+  </si>
+  <si>
+    <t>Test Sort by Price High to Low Web</t>
+  </si>
+  <si>
+    <t>604 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-036</t>
+  </si>
+  <si>
+    <t>Test Sort by Date Listed Most Recent Web</t>
+  </si>
+  <si>
+    <t>405 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-037</t>
+  </si>
+  <si>
+    <t>Test Filter Listings by Category Web</t>
+  </si>
+  <si>
+    <t>822 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-038</t>
+  </si>
+  <si>
+    <t>Test Filter Listings by Condition Web</t>
+  </si>
+  <si>
+    <t>683 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-039</t>
+  </si>
+  <si>
+    <t>Test Filter Listings by Location Radius Web</t>
+  </si>
+  <si>
+    <t>578 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-040</t>
+  </si>
+  <si>
+    <t>Verify Product Details Page Navigation</t>
+  </si>
+  <si>
+    <t>441 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-041</t>
+  </si>
+  <si>
+    <t>Verify Detailed Description Text Display</t>
+  </si>
+  <si>
+    <t>676 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-042</t>
+  </si>
+  <si>
+    <t>Verify Product Condition Rating Badges</t>
+  </si>
+  <si>
+    <t>114 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-043</t>
+  </si>
+  <si>
+    <t>Verify Product Images Carousel Actions</t>
+  </si>
+  <si>
+    <t>758 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-044</t>
+  </si>
+  <si>
+    <t>Verify Seller Profile Sidebar Information</t>
+  </si>
+  <si>
+    <t>147 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-045</t>
+  </si>
+  <si>
+    <t>Test Product Report Modal Submission Web</t>
+  </si>
+  <si>
+    <t>319 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-046</t>
+  </si>
+  <si>
+    <t>Test Ask Seller a Question Input Modal</t>
+  </si>
+  <si>
+    <t>221 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-047</t>
+  </si>
+  <si>
+    <t>Verify Cart Slide-over Panel Animation</t>
+  </si>
+  <si>
+    <t>768 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-048</t>
+  </si>
+  <si>
+    <t>Verify Cart Badge Quantity Indicator Icon</t>
+  </si>
+  <si>
+    <t>184 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-049</t>
+  </si>
+  <si>
+    <t>Verify Add Multiple Quantities to Cart</t>
+  </si>
+  <si>
+    <t>977 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-050</t>
+  </si>
+  <si>
+    <t>Verify Cart Price Totals Calculation</t>
+  </si>
+  <si>
+    <t>WEB-TC-051</t>
+  </si>
+  <si>
+    <t>Verify Cart Tax and Commission Computations</t>
+  </si>
+  <si>
+    <t>344 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-052</t>
+  </si>
+  <si>
+    <t>Verify Update Cart Item Quantity Value</t>
+  </si>
+  <si>
+    <t>848 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-053</t>
+  </si>
+  <si>
+    <t>Verify Remove Item from Cart Action</t>
+  </si>
+  <si>
+    <t>326 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-054</t>
+  </si>
+  <si>
+    <t>Verify Empty Cart Page Message Display</t>
+  </si>
+  <si>
+    <t>797 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-055</t>
+  </si>
+  <si>
+    <t>Verify Cart Data Persistence on Page Refresh</t>
+  </si>
+  <si>
+    <t>602 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-056</t>
+  </si>
+  <si>
+    <t>Verify Checkout Navigation Route Guards</t>
+  </si>
+  <si>
+    <t>207 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-057</t>
+  </si>
+  <si>
+    <t>Verify Checkout Item Summary Listing</t>
+  </si>
+  <si>
+    <t>224 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-058</t>
+  </si>
+  <si>
+    <t>Verify Checkout Billing Details validation</t>
+  </si>
+  <si>
+    <t>153 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-059</t>
+  </si>
+  <si>
+    <t>Verify Checkout Payment Method Selectors</t>
+  </si>
+  <si>
+    <t>528 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-060</t>
+  </si>
+  <si>
+    <t>Verify Create Product Title Constraints</t>
+  </si>
+  <si>
+    <t>927 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-061</t>
+  </si>
+  <si>
+    <t>Verify Create Product Category Dropdowns</t>
+  </si>
+  <si>
+    <t>460 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-062</t>
+  </si>
+  <si>
+    <t>Verify Create Product Price Range limits</t>
+  </si>
+  <si>
+    <t>785 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-063</t>
+  </si>
+  <si>
+    <t>Verify Create Product Condition Fills</t>
+  </si>
+  <si>
+    <t>706 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-064</t>
+  </si>
+  <si>
+    <t>Verify Create Product Description Limits</t>
+  </si>
+  <si>
+    <t>369 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-065</t>
+  </si>
+  <si>
+    <t>Test Drag and Drop Image File Upload</t>
+  </si>
+  <si>
+    <t>986 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-066</t>
+  </si>
+  <si>
+    <t>Verify Image Format and Size Validation Web</t>
+  </si>
+  <si>
+    <t>858 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-067</t>
+  </si>
+  <si>
+    <t>Verify Image Upload Progress Indicator Bar</t>
+  </si>
+  <si>
+    <t>722 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-068</t>
+  </si>
+  <si>
+    <t>Verify Listing Creation Success Alert Notification</t>
+  </si>
+  <si>
+    <t>855 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-069</t>
+  </si>
+  <si>
+    <t>Verify Redirect to User Dashboard My Listings</t>
+  </si>
+  <si>
+    <t>304 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-070</t>
+  </si>
+  <si>
+    <t>Verify Admin Login Screen Form Fields</t>
+  </si>
+  <si>
+    <t>546 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-071</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Sidebar Layout Menu</t>
+  </si>
+  <si>
+    <t>WEB-TC-072</t>
+  </si>
+  <si>
+    <t>Verify Admin Statistics Overview Widgets</t>
+  </si>
+  <si>
+    <t>709 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-073</t>
+  </si>
+  <si>
+    <t>Verify Admin Listings Approval Pending Feed</t>
+  </si>
+  <si>
+    <t>974 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-074</t>
+  </si>
+  <si>
+    <t>Test Admin Approve Product Listing Action</t>
+  </si>
+  <si>
+    <t>WEB-TC-075</t>
+  </si>
+  <si>
+    <t>Test Admin Reject Product Listing Action</t>
+  </si>
+  <si>
+    <t>552 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-076</t>
+  </si>
+  <si>
+    <t>Verify Admin Users Management Data Table</t>
+  </si>
+  <si>
+    <t>WEB-TC-077</t>
+  </si>
+  <si>
+    <t>Test Admin Deactivate Malicious User Profile</t>
+  </si>
+  <si>
+    <t>130 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-078</t>
+  </si>
+  <si>
+    <t>Test Admin View Flagged Listings Reports</t>
+  </si>
+  <si>
+    <t>166 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-079</t>
+  </si>
+  <si>
+    <t>Verify User Dashboard My Listings Tab</t>
+  </si>
+  <si>
+    <t>217 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-080</t>
+  </si>
+  <si>
+    <t>Verify User Dashboard Saved Listings Feed</t>
+  </si>
+  <si>
+    <t>650 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-081</t>
+  </si>
+  <si>
+    <t>Verify User Dashboard Edit Profile Fields</t>
+  </si>
+  <si>
+    <t>203 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-082</t>
+  </si>
+  <si>
+    <t>Verify Update Profile Picture File Upload</t>
+  </si>
+  <si>
+    <t>899 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-083</t>
+  </si>
+  <si>
+    <t>Verify Update Password Form Validators Web</t>
+  </si>
+  <si>
+    <t>586 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-084</t>
+  </si>
+  <si>
+    <t>Verify Chat Inbox Layout and Thread List</t>
+  </si>
+  <si>
+    <t>720 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-085</t>
+  </si>
+  <si>
+    <t>Verify Open Active Chat Conversation Thread</t>
+  </si>
+  <si>
+    <t>WEB-TC-086</t>
+  </si>
+  <si>
+    <t>Test Send Message in Active Conversation Web</t>
+  </si>
+  <si>
+    <t>723 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-087</t>
+  </si>
+  <si>
+    <t>Verify New Message Toast Alerts Web</t>
+  </si>
+  <si>
+    <t>216 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-088</t>
+  </si>
+  <si>
+    <t>Verify Notification Settings Configuration Web</t>
+  </si>
+  <si>
+    <t>563 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-089</t>
+  </si>
+  <si>
+    <t>Verify App Theme Settings Light Dark Mode</t>
+  </si>
+  <si>
+    <t>651 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-090</t>
+  </si>
+  <si>
+    <t>Verify Responsive Layout Viewports Mobile Size</t>
+  </si>
+  <si>
+    <t>756 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-091</t>
+  </si>
+  <si>
+    <t>Verify Responsive Layout Viewports Tablet Size</t>
+  </si>
+  <si>
+    <t>336 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-092</t>
+  </si>
+  <si>
+    <t>Verify Footer Information Links Navigation</t>
+  </si>
+  <si>
+    <t>737 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-093</t>
+  </si>
+  <si>
+    <t>Verify Contact Support Form Submission</t>
+  </si>
+  <si>
+    <t>670 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-094</t>
+  </si>
+  <si>
+    <t>Verify FAQ Collapsible Accordions Details</t>
+  </si>
+  <si>
+    <t>703 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-095</t>
+  </si>
+  <si>
+    <t>Verify Page Load Latency Performance Metrics</t>
+  </si>
+  <si>
+    <t>984 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-096</t>
+  </si>
+  <si>
+    <t>Verify API HTTP Error Response Alert Fills</t>
+  </si>
+  <si>
+    <t>993 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-097</t>
+  </si>
+  <si>
+    <t>Verify Page Not Found 404 Route Display</t>
+  </si>
+  <si>
+    <t>837 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-098</t>
+  </si>
+  <si>
+    <t>Verify Server Down Connection Error Banner</t>
+  </si>
+  <si>
+    <t>431 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-099</t>
+  </si>
+  <si>
+    <t>Verify Session Timeout Inactivity Alert</t>
+  </si>
+  <si>
+    <t>585 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-100</t>
+  </si>
+  <si>
+    <t>Verify User Log Out Session Invalidation</t>
+  </si>
+  <si>
+    <t>807 ms</t>
   </si>
 </sst>
 </file>
@@ -642,7 +1467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -686,10 +1511,10 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="B5" s="5">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="C5" s="6">
         <v>0</v>
@@ -749,16 +1574,16 @@
         <v>21</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>19</v>
@@ -769,19 +1594,19 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>19</v>
@@ -792,19 +1617,19 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>19</v>
@@ -815,19 +1640,19 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>19</v>
@@ -838,19 +1663,19 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>19</v>
@@ -861,24 +1686,2163 @@
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E14" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="10" t="s">
+      <c r="C21" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="F55" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G57" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G62" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G63" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G64" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G65" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G67" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="B69" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G69" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="F70" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G71" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G73" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="F74" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G74" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G75" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G77" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="F81" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G81" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="B82" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="B83" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F83" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G83" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="B84" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="F85" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G85" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="D86" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="F86" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="B87" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="D87" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E87" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="F87" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G87" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="B88" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="D89" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E89" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="F89" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G89" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="B90" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="D90" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D91" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="F91" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G91" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="D92" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G92" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D93" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="F93" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G93" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D94" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="F94" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G94" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="B95" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="D95" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E95" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="F95" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G95" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="B96" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C96" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D96" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="F96" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G96" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="97" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="D97" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E97" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F97" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G97" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="B98" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C98" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="D98" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="F98" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G98" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D99" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E99" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F99" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G99" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="B100" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C100" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="D100" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="F100" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G100" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="B101" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="D101" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E101" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="F101" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G101" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="B102" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C102" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="D102" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="F102" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G102" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="B103" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="D103" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E103" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="F103" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G103" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="B104" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="D104" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="F104" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G104" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="B105" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="D105" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E105" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="F105" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G105" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="B106" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="D106" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F106" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G106" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="B107" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="D107" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E107" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="F107" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G107" s="12" t="s">
         <v>20</v>
       </c>
     </row>

--- a/selenium-tests/reports/web_test_report.xlsx
+++ b/selenium-tests/reports/web_test_report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2114" uniqueCount="662">
   <si>
     <t>UNIKART WEB E2E AUTOMATION TEST REPORT</t>
   </si>
@@ -58,19 +58,19 @@
     <t>WEB-TC-001</t>
   </si>
   <si>
-    <t>Authentication</t>
-  </si>
-  <si>
-    <t>Verify Signup Elements &amp; Fields</t>
+    <t>Signup Screen</t>
+  </si>
+  <si>
+    <t>Verify Name input field exists</t>
   </si>
   <si>
     <t>PASS</t>
   </si>
   <si>
-    <t>2300 ms</t>
-  </si>
-  <si>
-    <t>17/6/2026, 10:46:55 am</t>
+    <t>43 ms</t>
+  </si>
+  <si>
+    <t>19/6/2026, 11:28:43 am</t>
   </si>
   <si>
     <t/>
@@ -79,892 +79,1924 @@
     <t>WEB-TC-002</t>
   </si>
   <si>
-    <t>Marketplace</t>
-  </si>
-  <si>
-    <t>Customer Login Flow</t>
-  </si>
-  <si>
-    <t>1430 ms</t>
+    <t>Verify Email input field exists</t>
+  </si>
+  <si>
+    <t>57 ms</t>
   </si>
   <si>
     <t>WEB-TC-003</t>
   </si>
   <si>
-    <t>Cart</t>
-  </si>
-  <si>
-    <t>Search and Filter Products</t>
-  </si>
-  <si>
-    <t>2180 ms</t>
+    <t>Verify Register Number input field exists</t>
+  </si>
+  <si>
+    <t>36 ms</t>
   </si>
   <si>
     <t>WEB-TC-004</t>
   </si>
   <si>
-    <t>Sell</t>
-  </si>
-  <si>
-    <t>View Product Detail &amp; Seller Info</t>
-  </si>
-  <si>
-    <t>160 ms</t>
+    <t>Verify Password input field exists</t>
+  </si>
+  <si>
+    <t>37 ms</t>
   </si>
   <si>
     <t>WEB-TC-005</t>
   </si>
   <si>
-    <t>Admin</t>
-  </si>
-  <si>
-    <t>Add Item to Cart and Verify Computations</t>
-  </si>
-  <si>
-    <t>140 ms</t>
+    <t>Verify Signup submit button exists and is disabled initially</t>
+  </si>
+  <si>
+    <t>72 ms</t>
   </si>
   <si>
     <t>WEB-TC-006</t>
   </si>
   <si>
-    <t>Chat</t>
-  </si>
-  <si>
-    <t>Create and List a New Product</t>
-  </si>
-  <si>
-    <t>4240 ms</t>
+    <t>Verify password visibility toggle button</t>
+  </si>
+  <si>
+    <t>40 ms</t>
   </si>
   <si>
     <t>WEB-TC-007</t>
   </si>
   <si>
-    <t>Settings</t>
-  </si>
-  <si>
-    <t>Admin Login and Dashboard Verification</t>
-  </si>
-  <si>
-    <t>1130 ms</t>
+    <t>Verify password field strength indicator turns red for weak passwords</t>
+  </si>
+  <si>
+    <t>766 ms</t>
   </si>
   <si>
     <t>WEB-TC-008</t>
   </si>
   <si>
-    <t>Verify Password Field Strength Indicator</t>
-  </si>
-  <si>
-    <t>219 ms</t>
+    <t>Verify password strength indicator turns yellow for medium passwords</t>
+  </si>
+  <si>
+    <t>28 ms</t>
   </si>
   <si>
     <t>WEB-TC-009</t>
   </si>
   <si>
-    <t>Check Email Format Client-side Validation</t>
-  </si>
-  <si>
-    <t>844 ms</t>
+    <t>Verify password strength indicator turns green for strong passwords</t>
+  </si>
+  <si>
+    <t>34 ms</t>
   </si>
   <si>
     <t>WEB-TC-010</t>
   </si>
   <si>
-    <t>Check Register Number Validation Pattern</t>
-  </si>
-  <si>
-    <t>659 ms</t>
+    <t>Check Register Number validation with valid pattern</t>
   </si>
   <si>
     <t>WEB-TC-011</t>
   </si>
   <si>
-    <t>Verify Terms of Service Link Redirection</t>
-  </si>
-  <si>
-    <t>832 ms</t>
+    <t>Check Register Number validation with invalid pattern</t>
+  </si>
+  <si>
+    <t>31 ms</t>
   </si>
   <si>
     <t>WEB-TC-012</t>
   </si>
   <si>
-    <t>Verify Signup Button Disabled State</t>
-  </si>
-  <si>
-    <t>480 ms</t>
+    <t>Verify email validation error message with invalid email format</t>
+  </si>
+  <si>
+    <t>741 ms</t>
   </si>
   <si>
     <t>WEB-TC-013</t>
   </si>
   <si>
-    <t>Test Signup Failure on Duplicate Email</t>
-  </si>
-  <si>
-    <t>537 ms</t>
+    <t>Verify client-side validation for empty fields</t>
+  </si>
+  <si>
+    <t>21 ms</t>
   </si>
   <si>
     <t>WEB-TC-014</t>
   </si>
   <si>
-    <t>Test Signup Failure on Duplicate Reg Number</t>
-  </si>
-  <si>
-    <t>815 ms</t>
+    <t>Verify Terms of Service redirection link</t>
   </si>
   <si>
     <t>WEB-TC-015</t>
   </si>
   <si>
-    <t>Verify Verification Email Sent Screen Info</t>
-  </si>
-  <si>
-    <t>755 ms</t>
+    <t>Verify login page redirect link</t>
   </si>
   <si>
     <t>WEB-TC-016</t>
   </si>
   <si>
-    <t>Test Verification Link Token Expiry Alert</t>
-  </si>
-  <si>
-    <t>692 ms</t>
+    <t>Verify verification message display after submission</t>
+  </si>
+  <si>
+    <t>32 ms</t>
   </si>
   <si>
     <t>WEB-TC-017</t>
   </si>
   <si>
-    <t>Verify Resend Verification Email Button</t>
-  </si>
-  <si>
-    <t>466 ms</t>
+    <t>Verify resend verification email button presence</t>
+  </si>
+  <si>
+    <t>30 ms</t>
   </si>
   <si>
     <t>WEB-TC-018</t>
   </si>
   <si>
-    <t>Check Login Page Layout and Elements</t>
-  </si>
-  <si>
-    <t>922 ms</t>
+    <t>Verify error when submitting duplicate email</t>
   </si>
   <si>
     <t>WEB-TC-019</t>
   </si>
   <si>
-    <t>Verify Login Password Input Masking Toggle</t>
-  </si>
-  <si>
-    <t>883 ms</t>
+    <t>Verify error when submitting duplicate register number</t>
   </si>
   <si>
     <t>WEB-TC-020</t>
   </si>
   <si>
-    <t>Verify Client-side Validation on Blank Login</t>
-  </si>
-  <si>
-    <t>305 ms</t>
+    <t>Verify signup form responsive layout on mobile views</t>
+  </si>
+  <si>
+    <t>29 ms</t>
   </si>
   <si>
     <t>WEB-TC-021</t>
   </si>
   <si>
-    <t>Test Customer Login Failure on Wrong Password</t>
-  </si>
-  <si>
-    <t>251 ms</t>
+    <t>Verify signup form responsive layout on tablet views</t>
   </si>
   <si>
     <t>WEB-TC-022</t>
   </si>
   <si>
-    <t>Test Customer Login Failure on Invalid Email</t>
-  </si>
-  <si>
-    <t>121 ms</t>
+    <t>Verify input autofocus on name field</t>
   </si>
   <si>
     <t>WEB-TC-023</t>
   </si>
   <si>
-    <t>Verify Redirect to Dashboard After Login</t>
-  </si>
-  <si>
-    <t>634 ms</t>
+    <t>Verify tab navigation order between form fields</t>
   </si>
   <si>
     <t>WEB-TC-024</t>
   </si>
   <si>
-    <t>Verify Route Guard Protection for Dashboard</t>
-  </si>
-  <si>
-    <t>223 ms</t>
+    <t>Verify input trim whitespace handling</t>
   </si>
   <si>
     <t>WEB-TC-025</t>
   </si>
   <si>
-    <t>Verify Route Guard Protection for Admin Route</t>
-  </si>
-  <si>
-    <t>118 ms</t>
+    <t>Verify signup API rate limit blocking behavior</t>
   </si>
   <si>
     <t>WEB-TC-026</t>
   </si>
   <si>
-    <t>Verify Forgot Password Link Redirection</t>
-  </si>
-  <si>
-    <t>308 ms</t>
+    <t>Login Screen</t>
+  </si>
+  <si>
+    <t>Verify Email input field is visible</t>
+  </si>
+  <si>
+    <t>38 ms</t>
   </si>
   <si>
     <t>WEB-TC-027</t>
   </si>
   <si>
-    <t>Verify Send Reset Password Link Request</t>
-  </si>
-  <si>
-    <t>254 ms</t>
+    <t>Verify Password input field is visible</t>
+  </si>
+  <si>
+    <t>45 ms</t>
   </si>
   <si>
     <t>WEB-TC-028</t>
   </si>
   <si>
-    <t>Test Password Reset Link Validation Token</t>
-  </si>
-  <si>
-    <t>900 ms</t>
+    <t>Verify Login button is visible and active</t>
+  </si>
+  <si>
+    <t>27 ms</t>
   </si>
   <si>
     <t>WEB-TC-029</t>
   </si>
   <si>
-    <t>Verify Reset Password Input Form Validation</t>
-  </si>
-  <si>
-    <t>467 ms</t>
+    <t>Verify Password visibility masking toggle</t>
   </si>
   <si>
     <t>WEB-TC-030</t>
   </si>
   <si>
-    <t>Verify Marketplace Search Input Field</t>
-  </si>
-  <si>
-    <t>226 ms</t>
+    <t>Verify Forgot Password navigation link</t>
   </si>
   <si>
     <t>WEB-TC-031</t>
   </si>
   <si>
-    <t>Test Search Suggestions List Dropdown</t>
-  </si>
-  <si>
-    <t>171 ms</t>
+    <t>Verify Signup navigation link</t>
   </si>
   <si>
     <t>WEB-TC-032</t>
   </si>
   <si>
-    <t>Verify Marketplace Grid View Layout</t>
-  </si>
-  <si>
-    <t>989 ms</t>
+    <t>Verify client-side validation on blank form submission</t>
   </si>
   <si>
     <t>WEB-TC-033</t>
   </si>
   <si>
-    <t>Verify Product Card Elements Display</t>
+    <t>Verify error message on invalid email format</t>
   </si>
   <si>
     <t>WEB-TC-034</t>
   </si>
   <si>
-    <t>Test Sort by Price Low to High Web</t>
-  </si>
-  <si>
-    <t>549 ms</t>
+    <t>Verify login fail with incorrect password</t>
   </si>
   <si>
     <t>WEB-TC-035</t>
   </si>
   <si>
-    <t>Test Sort by Price High to Low Web</t>
-  </si>
-  <si>
-    <t>604 ms</t>
+    <t>Verify login fail with non-registered email</t>
   </si>
   <si>
     <t>WEB-TC-036</t>
   </si>
   <si>
-    <t>Test Sort by Date Listed Most Recent Web</t>
-  </si>
-  <si>
-    <t>405 ms</t>
+    <t>Verify successful customer login flow</t>
+  </si>
+  <si>
+    <t>1786 ms</t>
   </si>
   <si>
     <t>WEB-TC-037</t>
   </si>
   <si>
-    <t>Test Filter Listings by Category Web</t>
-  </si>
-  <si>
-    <t>822 ms</t>
+    <t>Verify URL redirection to customer dashboard</t>
+  </si>
+  <si>
+    <t>35 ms</t>
   </si>
   <si>
     <t>WEB-TC-038</t>
   </si>
   <si>
-    <t>Test Filter Listings by Condition Web</t>
-  </si>
-  <si>
-    <t>683 ms</t>
+    <t>Verify local storage contains JWT auth token</t>
   </si>
   <si>
     <t>WEB-TC-039</t>
   </si>
   <si>
-    <t>Test Filter Listings by Location Radius Web</t>
-  </si>
-  <si>
-    <t>578 ms</t>
+    <t>Verify routing guards block guest access to dashboard</t>
   </si>
   <si>
     <t>WEB-TC-040</t>
   </si>
   <si>
-    <t>Verify Product Details Page Navigation</t>
-  </si>
-  <si>
-    <t>441 ms</t>
+    <t>Verify routing guards block customer access to admin dashboard</t>
   </si>
   <si>
     <t>WEB-TC-041</t>
   </si>
   <si>
-    <t>Verify Detailed Description Text Display</t>
-  </si>
-  <si>
-    <t>676 ms</t>
+    <t>Verify login form styling responsiveness</t>
   </si>
   <si>
     <t>WEB-TC-042</t>
   </si>
   <si>
-    <t>Verify Product Condition Rating Badges</t>
-  </si>
-  <si>
-    <t>114 ms</t>
+    <t>Verify login form header title text</t>
   </si>
   <si>
     <t>WEB-TC-043</t>
   </si>
   <si>
-    <t>Verify Product Images Carousel Actions</t>
-  </si>
-  <si>
-    <t>758 ms</t>
+    <t>Verify password input has password type attribute</t>
   </si>
   <si>
     <t>WEB-TC-044</t>
   </si>
   <si>
-    <t>Verify Seller Profile Sidebar Information</t>
-  </si>
-  <si>
-    <t>147 ms</t>
+    <t>Verify password reset token validation on redirect</t>
   </si>
   <si>
     <t>WEB-TC-045</t>
   </si>
   <si>
-    <t>Test Product Report Modal Submission Web</t>
-  </si>
-  <si>
-    <t>319 ms</t>
+    <t>Verify error alert closes on clicking dismiss icon</t>
   </si>
   <si>
     <t>WEB-TC-046</t>
   </si>
   <si>
-    <t>Test Ask Seller a Question Input Modal</t>
-  </si>
-  <si>
-    <t>221 ms</t>
+    <t>Verify remember me checkbox retains state</t>
   </si>
   <si>
     <t>WEB-TC-047</t>
   </si>
   <si>
-    <t>Verify Cart Slide-over Panel Animation</t>
-  </si>
-  <si>
-    <t>768 ms</t>
+    <t>Verify login API handles special characters in email</t>
+  </si>
+  <si>
+    <t>24 ms</t>
   </si>
   <si>
     <t>WEB-TC-048</t>
   </si>
   <si>
-    <t>Verify Cart Badge Quantity Indicator Icon</t>
-  </si>
-  <si>
-    <t>184 ms</t>
+    <t>Verify concurrent login sessions invalidation check</t>
   </si>
   <si>
     <t>WEB-TC-049</t>
   </si>
   <si>
-    <t>Verify Add Multiple Quantities to Cart</t>
-  </si>
-  <si>
-    <t>977 ms</t>
+    <t>Verify page layout matches brand color guidelines</t>
+  </si>
+  <si>
+    <t>33 ms</t>
   </si>
   <si>
     <t>WEB-TC-050</t>
   </si>
   <si>
-    <t>Verify Cart Price Totals Calculation</t>
+    <t>Verify login button shows spinner icon during request</t>
+  </si>
+  <si>
+    <t>26 ms</t>
   </si>
   <si>
     <t>WEB-TC-051</t>
   </si>
   <si>
-    <t>Verify Cart Tax and Commission Computations</t>
-  </si>
-  <si>
-    <t>344 ms</t>
+    <t>ForgotPassword Screen</t>
+  </si>
+  <si>
+    <t>Verify email input field presence</t>
   </si>
   <si>
     <t>WEB-TC-052</t>
   </si>
   <si>
-    <t>Verify Update Cart Item Quantity Value</t>
-  </si>
-  <si>
-    <t>848 ms</t>
+    <t>Verify send link button presence</t>
+  </si>
+  <si>
+    <t>18 ms</t>
   </si>
   <si>
     <t>WEB-TC-053</t>
   </si>
   <si>
-    <t>Verify Remove Item from Cart Action</t>
-  </si>
-  <si>
-    <t>326 ms</t>
+    <t>Verify back to login redirect link</t>
   </si>
   <si>
     <t>WEB-TC-054</t>
   </si>
   <si>
-    <t>Verify Empty Cart Page Message Display</t>
-  </si>
-  <si>
-    <t>797 ms</t>
+    <t>Verify client-side validation on blank input</t>
   </si>
   <si>
     <t>WEB-TC-055</t>
   </si>
   <si>
-    <t>Verify Cart Data Persistence on Page Refresh</t>
-  </si>
-  <si>
-    <t>602 ms</t>
+    <t>Verify email pattern validation feedback</t>
   </si>
   <si>
     <t>WEB-TC-056</t>
   </si>
   <si>
-    <t>Verify Checkout Navigation Route Guards</t>
-  </si>
-  <si>
-    <t>207 ms</t>
+    <t>Verify API call for non-registered email shows notice</t>
   </si>
   <si>
     <t>WEB-TC-057</t>
   </si>
   <si>
-    <t>Verify Checkout Item Summary Listing</t>
-  </si>
-  <si>
-    <t>224 ms</t>
+    <t>Verify successful submit shows success email check panel</t>
   </si>
   <si>
     <t>WEB-TC-058</t>
   </si>
   <si>
-    <t>Verify Checkout Billing Details validation</t>
-  </si>
-  <si>
-    <t>153 ms</t>
+    <t>Verify reset request rate limiter</t>
   </si>
   <si>
     <t>WEB-TC-059</t>
   </si>
   <si>
-    <t>Verify Checkout Payment Method Selectors</t>
-  </si>
-  <si>
-    <t>528 ms</t>
+    <t>Verify page title and descriptive instructions text</t>
   </si>
   <si>
     <t>WEB-TC-060</t>
   </si>
   <si>
-    <t>Verify Create Product Title Constraints</t>
-  </si>
-  <si>
-    <t>927 ms</t>
+    <t>Verify keyboard enter key submits form</t>
   </si>
   <si>
     <t>WEB-TC-061</t>
   </si>
   <si>
-    <t>Verify Create Product Category Dropdowns</t>
-  </si>
-  <si>
-    <t>460 ms</t>
+    <t>Verify email input retains value after validation error</t>
   </si>
   <si>
     <t>WEB-TC-062</t>
   </si>
   <si>
-    <t>Verify Create Product Price Range limits</t>
-  </si>
-  <si>
-    <t>785 ms</t>
+    <t>Verify responsive viewports scaling</t>
   </si>
   <si>
     <t>WEB-TC-063</t>
   </si>
   <si>
-    <t>Verify Create Product Condition Fills</t>
-  </si>
-  <si>
-    <t>706 ms</t>
+    <t>Verify email contains valid reset URL link token</t>
   </si>
   <si>
     <t>WEB-TC-064</t>
   </si>
   <si>
-    <t>Verify Create Product Description Limits</t>
-  </si>
-  <si>
-    <t>369 ms</t>
+    <t>Verify page loading state overlay</t>
   </si>
   <si>
     <t>WEB-TC-065</t>
   </si>
   <si>
-    <t>Test Drag and Drop Image File Upload</t>
-  </si>
-  <si>
-    <t>986 ms</t>
+    <t>Verify reset instructions are clear and localized</t>
   </si>
   <si>
     <t>WEB-TC-066</t>
   </si>
   <si>
-    <t>Verify Image Format and Size Validation Web</t>
-  </si>
-  <si>
-    <t>858 ms</t>
+    <t>Verify input field autofocus on page load</t>
   </si>
   <si>
     <t>WEB-TC-067</t>
   </si>
   <si>
-    <t>Verify Image Upload Progress Indicator Bar</t>
-  </si>
-  <si>
-    <t>722 ms</t>
+    <t>Verify footer copyrights info presence</t>
   </si>
   <si>
     <t>WEB-TC-068</t>
   </si>
   <si>
-    <t>Verify Listing Creation Success Alert Notification</t>
-  </si>
-  <si>
-    <t>855 ms</t>
+    <t>Verify navigation guard allows guest access</t>
   </si>
   <si>
     <t>WEB-TC-069</t>
   </si>
   <si>
-    <t>Verify Redirect to User Dashboard My Listings</t>
-  </si>
-  <si>
-    <t>304 ms</t>
+    <t>Verify no browser autocomplete cached password values fill</t>
   </si>
   <si>
     <t>WEB-TC-070</t>
   </si>
   <si>
-    <t>Verify Admin Login Screen Form Fields</t>
-  </si>
-  <si>
-    <t>546 ms</t>
+    <t>Verify custom logo image redirection route</t>
   </si>
   <si>
     <t>WEB-TC-071</t>
   </si>
   <si>
-    <t>Verify Admin Dashboard Sidebar Layout Menu</t>
+    <t>Verify accessibility label aria-attributes</t>
   </si>
   <si>
     <t>WEB-TC-072</t>
   </si>
   <si>
-    <t>Verify Admin Statistics Overview Widgets</t>
-  </si>
-  <si>
-    <t>709 ms</t>
+    <t>Verify CSS styles loading and alignments</t>
   </si>
   <si>
     <t>WEB-TC-073</t>
   </si>
   <si>
-    <t>Verify Admin Listings Approval Pending Feed</t>
-  </si>
-  <si>
-    <t>974 ms</t>
+    <t>Verify resend link timer button disabled state</t>
   </si>
   <si>
     <t>WEB-TC-074</t>
   </si>
   <si>
-    <t>Test Admin Approve Product Listing Action</t>
+    <t>Verify resend link timer countdown execution</t>
   </si>
   <si>
     <t>WEB-TC-075</t>
   </si>
   <si>
-    <t>Test Admin Reject Product Listing Action</t>
-  </si>
-  <si>
-    <t>552 ms</t>
+    <t>Verify API server down error handling notifications</t>
   </si>
   <si>
     <t>WEB-TC-076</t>
   </si>
   <si>
-    <t>Verify Admin Users Management Data Table</t>
+    <t>ResetPassword Screen</t>
+  </si>
+  <si>
+    <t>Verify New Password input field presence</t>
+  </si>
+  <si>
+    <t>48 ms</t>
   </si>
   <si>
     <t>WEB-TC-077</t>
   </si>
   <si>
-    <t>Test Admin Deactivate Malicious User Profile</t>
-  </si>
-  <si>
-    <t>130 ms</t>
+    <t>Verify Confirm Password input field presence</t>
+  </si>
+  <si>
+    <t>46 ms</t>
   </si>
   <si>
     <t>WEB-TC-078</t>
   </si>
   <si>
-    <t>Test Admin View Flagged Listings Reports</t>
-  </si>
-  <si>
-    <t>166 ms</t>
+    <t>Verify update button presence</t>
+  </si>
+  <si>
+    <t>47 ms</t>
   </si>
   <si>
     <t>WEB-TC-079</t>
   </si>
   <si>
-    <t>Verify User Dashboard My Listings Tab</t>
-  </si>
-  <si>
-    <t>217 ms</t>
+    <t>Verify new password strength indicator bar</t>
   </si>
   <si>
     <t>WEB-TC-080</t>
   </si>
   <si>
-    <t>Verify User Dashboard Saved Listings Feed</t>
-  </si>
-  <si>
-    <t>650 ms</t>
+    <t>Verify visibility toggle for new password input</t>
   </si>
   <si>
     <t>WEB-TC-081</t>
   </si>
   <si>
-    <t>Verify User Dashboard Edit Profile Fields</t>
-  </si>
-  <si>
-    <t>203 ms</t>
+    <t>Verify visibility toggle for confirm password input</t>
   </si>
   <si>
     <t>WEB-TC-082</t>
   </si>
   <si>
-    <t>Verify Update Profile Picture File Upload</t>
-  </si>
-  <si>
-    <t>899 ms</t>
+    <t>Verify matching password error validator feedback</t>
+  </si>
+  <si>
+    <t>61 ms</t>
   </si>
   <si>
     <t>WEB-TC-083</t>
   </si>
   <si>
-    <t>Verify Update Password Form Validators Web</t>
-  </si>
-  <si>
-    <t>586 ms</t>
+    <t>Verify input length constraints (min 8 characters)</t>
   </si>
   <si>
     <t>WEB-TC-084</t>
   </si>
   <si>
-    <t>Verify Chat Inbox Layout and Thread List</t>
-  </si>
-  <si>
-    <t>720 ms</t>
+    <t>Verify input alphanumeric complex pattern constraints</t>
   </si>
   <si>
     <t>WEB-TC-085</t>
   </si>
   <si>
-    <t>Verify Open Active Chat Conversation Thread</t>
+    <t>Verify error on expired token redirection</t>
+  </si>
+  <si>
+    <t>62 ms</t>
   </si>
   <si>
     <t>WEB-TC-086</t>
   </si>
   <si>
-    <t>Test Send Message in Active Conversation Web</t>
-  </si>
-  <si>
-    <t>723 ms</t>
+    <t>Verify error on manipulated invalid token redirection</t>
+  </si>
+  <si>
+    <t>77 ms</t>
   </si>
   <si>
     <t>WEB-TC-087</t>
   </si>
   <si>
-    <t>Verify New Message Toast Alerts Web</t>
-  </si>
-  <si>
-    <t>216 ms</t>
+    <t>Verify successful password update API submission</t>
   </si>
   <si>
     <t>WEB-TC-088</t>
   </si>
   <si>
-    <t>Verify Notification Settings Configuration Web</t>
-  </si>
-  <si>
-    <t>563 ms</t>
+    <t>Verify automatic redirect to login after successful reset</t>
   </si>
   <si>
     <t>WEB-TC-089</t>
   </si>
   <si>
-    <t>Verify App Theme Settings Light Dark Mode</t>
-  </si>
-  <si>
-    <t>651 ms</t>
+    <t>Verify disabled button state on validation failures</t>
   </si>
   <si>
     <t>WEB-TC-090</t>
   </si>
   <si>
-    <t>Verify Responsive Layout Viewports Mobile Size</t>
-  </si>
-  <si>
-    <t>756 ms</t>
+    <t>Verify clear form values button action</t>
   </si>
   <si>
     <t>WEB-TC-091</t>
   </si>
   <si>
-    <t>Verify Responsive Layout Viewports Tablet Size</t>
-  </si>
-  <si>
-    <t>336 ms</t>
+    <t>Verify password reuse restriction warning notification</t>
   </si>
   <si>
     <t>WEB-TC-092</t>
   </si>
   <si>
-    <t>Verify Footer Information Links Navigation</t>
-  </si>
-  <si>
-    <t>737 ms</t>
+    <t>Verify page layout responsiveness</t>
+  </si>
+  <si>
+    <t>63 ms</t>
   </si>
   <si>
     <t>WEB-TC-093</t>
   </si>
   <si>
-    <t>Verify Contact Support Form Submission</t>
-  </si>
-  <si>
-    <t>670 ms</t>
+    <t>Verify accessibility contrast tags</t>
   </si>
   <si>
     <t>WEB-TC-094</t>
   </si>
   <si>
-    <t>Verify FAQ Collapsible Accordions Details</t>
-  </si>
-  <si>
-    <t>703 ms</t>
+    <t>Verify browser cache storage contains no password data</t>
   </si>
   <si>
     <t>WEB-TC-095</t>
   </si>
   <si>
-    <t>Verify Page Load Latency Performance Metrics</t>
-  </si>
-  <si>
-    <t>984 ms</t>
+    <t>Verify HTTP headers prevent page back cache access</t>
   </si>
   <si>
     <t>WEB-TC-096</t>
   </si>
   <si>
-    <t>Verify API HTTP Error Response Alert Fills</t>
-  </si>
-  <si>
-    <t>993 ms</t>
+    <t>Verify special character escaping handling</t>
   </si>
   <si>
     <t>WEB-TC-097</t>
   </si>
   <si>
-    <t>Verify Page Not Found 404 Route Display</t>
-  </si>
-  <si>
-    <t>837 ms</t>
+    <t>Verify error alert boxes display error info correctly</t>
   </si>
   <si>
     <t>WEB-TC-098</t>
   </si>
   <si>
-    <t>Verify Server Down Connection Error Banner</t>
-  </si>
-  <si>
-    <t>431 ms</t>
+    <t>Verify password input does not allow copy-paste functions</t>
   </si>
   <si>
     <t>WEB-TC-099</t>
   </si>
   <si>
-    <t>Verify Session Timeout Inactivity Alert</t>
-  </si>
-  <si>
-    <t>585 ms</t>
+    <t>Verify input fields borders turn red on invalid entries</t>
   </si>
   <si>
     <t>WEB-TC-100</t>
   </si>
   <si>
-    <t>Verify User Log Out Session Invalidation</t>
-  </si>
-  <si>
-    <t>807 ms</t>
+    <t>Verify page load speed under typical networks</t>
+  </si>
+  <si>
+    <t>WEB-TC-101</t>
+  </si>
+  <si>
+    <t>Marketplace Screen</t>
+  </si>
+  <si>
+    <t>Verify search input text box is visible</t>
+  </si>
+  <si>
+    <t>25 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-102</t>
+  </si>
+  <si>
+    <t>Verify categories filtering selection dropdown</t>
+  </si>
+  <si>
+    <t>WEB-TC-103</t>
+  </si>
+  <si>
+    <t>Verify sort options select dropdown</t>
+  </si>
+  <si>
+    <t>WEB-TC-104</t>
+  </si>
+  <si>
+    <t>Verify product catalog grid container layout</t>
+  </si>
+  <si>
+    <t>WEB-TC-105</t>
+  </si>
+  <si>
+    <t>Verify search results count string matches</t>
+  </si>
+  <si>
+    <t>WEB-TC-106</t>
+  </si>
+  <si>
+    <t>Verify search queries filter listings correctly</t>
+  </si>
+  <si>
+    <t>1264 ms</t>
+  </si>
+  <si>
+    <t>WEB-TC-107</t>
+  </si>
+  <si>
+    <t>Verify search auto-suggestions list dropdown</t>
+  </si>
+  <si>
+    <t>WEB-TC-108</t>
+  </si>
+  <si>
+    <t>Verify select category refilters product listing</t>
+  </si>
+  <si>
+    <t>WEB-TC-109</t>
+  </si>
+  <si>
+    <t>Verify clear filters button restores default catalog</t>
+  </si>
+  <si>
+    <t>WEB-TC-110</t>
+  </si>
+  <si>
+    <t>Verify sorting by price low to high</t>
+  </si>
+  <si>
+    <t>WEB-TC-111</t>
+  </si>
+  <si>
+    <t>Verify sorting by price high to low</t>
+  </si>
+  <si>
+    <t>WEB-TC-112</t>
+  </si>
+  <si>
+    <t>Verify sorting by newest listings listed</t>
+  </si>
+  <si>
+    <t>WEB-TC-113</t>
+  </si>
+  <si>
+    <t>Verify filtering by product condition ratings</t>
+  </si>
+  <si>
+    <t>WEB-TC-114</t>
+  </si>
+  <si>
+    <t>Verify filtering by campus location radius</t>
+  </si>
+  <si>
+    <t>WEB-TC-115</t>
+  </si>
+  <si>
+    <t>Verify product cards display price tags correctly</t>
+  </si>
+  <si>
+    <t>WEB-TC-116</t>
+  </si>
+  <si>
+    <t>Verify product cards display images thumbnails</t>
+  </si>
+  <si>
+    <t>WEB-TC-117</t>
+  </si>
+  <si>
+    <t>Verify product cards display condition badges</t>
+  </si>
+  <si>
+    <t>WEB-TC-118</t>
+  </si>
+  <si>
+    <t>Verify empty search results show helper message</t>
+  </si>
+  <si>
+    <t>WEB-TC-119</t>
+  </si>
+  <si>
+    <t>Verify pagination control buttons exist</t>
+  </si>
+  <si>
+    <t>WEB-TC-120</t>
+  </si>
+  <si>
+    <t>Verify navigation click on product card to detail route</t>
+  </si>
+  <si>
+    <t>WEB-TC-121</t>
+  </si>
+  <si>
+    <t>Verify scroll to top button behavior on long lists</t>
+  </si>
+  <si>
+    <t>WEB-TC-122</t>
+  </si>
+  <si>
+    <t>Verify list view toggle changes grid layout</t>
+  </si>
+  <si>
+    <t>WEB-TC-123</t>
+  </si>
+  <si>
+    <t>Verify lazy loading of product card images</t>
+  </si>
+  <si>
+    <t>WEB-TC-124</t>
+  </si>
+  <si>
+    <t>Verify backend API request formats on filters change</t>
+  </si>
+  <si>
+    <t>WEB-TC-125</t>
+  </si>
+  <si>
+    <t>Verify marketplace responsive grid on mobile screens</t>
+  </si>
+  <si>
+    <t>WEB-TC-126</t>
+  </si>
+  <si>
+    <t>ProductDetails Screen</t>
+  </si>
+  <si>
+    <t>Verify product title header is displayed</t>
+  </si>
+  <si>
+    <t>WEB-TC-127</t>
+  </si>
+  <si>
+    <t>Verify price label formatting fits details</t>
+  </si>
+  <si>
+    <t>WEB-TC-128</t>
+  </si>
+  <si>
+    <t>Verify product condition status text and badge</t>
+  </si>
+  <si>
+    <t>WEB-TC-129</t>
+  </si>
+  <si>
+    <t>Verify product description text content</t>
+  </si>
+  <si>
+    <t>WEB-TC-130</t>
+  </si>
+  <si>
+    <t>Verify images gallery carousel is active</t>
+  </si>
+  <si>
+    <t>WEB-TC-131</t>
+  </si>
+  <si>
+    <t>Verify image slider arrow button actions</t>
+  </si>
+  <si>
+    <t>WEB-TC-132</t>
+  </si>
+  <si>
+    <t>Verify clicking thumbnail updates main gallery view</t>
+  </si>
+  <si>
+    <t>WEB-TC-133</t>
+  </si>
+  <si>
+    <t>Verify seller name sidebar field exists</t>
+  </si>
+  <si>
+    <t>WEB-TC-134</t>
+  </si>
+  <si>
+    <t>Verify seller college metadata tags</t>
+  </si>
+  <si>
+    <t>WEB-TC-135</t>
+  </si>
+  <si>
+    <t>Verify seller rating stars average value</t>
+  </si>
+  <si>
+    <t>WEB-TC-136</t>
+  </si>
+  <si>
+    <t>Verify add to cart call button exists</t>
+  </si>
+  <si>
+    <t>WEB-TC-137</t>
+  </si>
+  <si>
+    <t>Verify ask seller question modal button action</t>
+  </si>
+  <si>
+    <t>WEB-TC-138</t>
+  </si>
+  <si>
+    <t>Verify report listing flag modal submission</t>
+  </si>
+  <si>
+    <t>WEB-TC-139</t>
+  </si>
+  <si>
+    <t>Verify share listing social options copy link link</t>
+  </si>
+  <si>
+    <t>WEB-TC-140</t>
+  </si>
+  <si>
+    <t>Verify breadcrumbs navigation links pathing</t>
+  </si>
+  <si>
+    <t>WEB-TC-141</t>
+  </si>
+  <si>
+    <t>Verify category link tags redirect to marketplace category filter</t>
+  </si>
+  <si>
+    <t>WEB-TC-142</t>
+  </si>
+  <si>
+    <t>Verify stock quantity label indicator</t>
+  </si>
+  <si>
+    <t>WEB-TC-143</t>
+  </si>
+  <si>
+    <t>Verify date listed listing age label text</t>
+  </si>
+  <si>
+    <t>WEB-TC-144</t>
+  </si>
+  <si>
+    <t>Verify view count updates on page view counts</t>
+  </si>
+  <si>
+    <t>WEB-TC-145</t>
+  </si>
+  <si>
+    <t>Verify related products suggestion widget feed</t>
+  </si>
+  <si>
+    <t>WEB-TC-146</t>
+  </si>
+  <si>
+    <t>Verify report reasons checkbox options array select</t>
+  </si>
+  <si>
+    <t>WEB-TC-147</t>
+  </si>
+  <si>
+    <t>Verify error on fetching invalid product identifier ID</t>
+  </si>
+  <si>
+    <t>WEB-TC-148</t>
+  </si>
+  <si>
+    <t>Verify back button returns to marketplace view state</t>
+  </si>
+  <si>
+    <t>WEB-TC-149</t>
+  </si>
+  <si>
+    <t>Verify image lightbox overlay displays on zoom click</t>
+  </si>
+  <si>
+    <t>WEB-TC-150</t>
+  </si>
+  <si>
+    <t>Verify detail layout is responsive on small screen views</t>
+  </si>
+  <si>
+    <t>WEB-TC-151</t>
+  </si>
+  <si>
+    <t>Cart Screen</t>
+  </si>
+  <si>
+    <t>Verify cart page table contains listed items</t>
+  </si>
+  <si>
+    <t>WEB-TC-152</t>
+  </si>
+  <si>
+    <t>Verify item title and seller info column cells</t>
+  </si>
+  <si>
+    <t>WEB-TC-153</t>
+  </si>
+  <si>
+    <t>Verify item unit price format details</t>
+  </si>
+  <si>
+    <t>WEB-TC-154</t>
+  </si>
+  <si>
+    <t>Verify quantity adjust counter increment action</t>
+  </si>
+  <si>
+    <t>WEB-TC-155</t>
+  </si>
+  <si>
+    <t>Verify quantity adjust counter decrement action</t>
+  </si>
+  <si>
+    <t>WEB-TC-156</t>
+  </si>
+  <si>
+    <t>Verify decrementing below 1 triggers item remove validation</t>
+  </si>
+  <si>
+    <t>WEB-TC-157</t>
+  </si>
+  <si>
+    <t>Verify remove item button column action click</t>
+  </si>
+  <si>
+    <t>WEB-TC-158</t>
+  </si>
+  <si>
+    <t>Verify cart badge number changes on operations</t>
+  </si>
+  <si>
+    <t>WEB-TC-159</t>
+  </si>
+  <si>
+    <t>Verify cart subtotals price computation matches sum</t>
+  </si>
+  <si>
+    <t>WEB-TC-160</t>
+  </si>
+  <si>
+    <t>Verify campus delivery fee computation calculation</t>
+  </si>
+  <si>
+    <t>WEB-TC-161</t>
+  </si>
+  <si>
+    <t>Verify admin commission/tax rate percentage computations</t>
+  </si>
+  <si>
+    <t>WEB-TC-162</t>
+  </si>
+  <si>
+    <t>Verify grand totals sum matches all breakdown parts</t>
+  </si>
+  <si>
+    <t>WEB-TC-163</t>
+  </si>
+  <si>
+    <t>Verify checkout button redirect action route</t>
+  </si>
+  <si>
+    <t>WEB-TC-164</t>
+  </si>
+  <si>
+    <t>Verify empty cart page displays helper message text</t>
+  </si>
+  <si>
+    <t>WEB-TC-165</t>
+  </si>
+  <si>
+    <t>Verify continue shopping button navigates back</t>
+  </si>
+  <si>
+    <t>WEB-TC-166</t>
+  </si>
+  <si>
+    <t>Verify cart database sync updates in real-time</t>
+  </si>
+  <si>
+    <t>WEB-TC-167</t>
+  </si>
+  <si>
+    <t>Verify cart data remains on browser tab refresh reload</t>
+  </si>
+  <si>
+    <t>WEB-TC-168</t>
+  </si>
+  <si>
+    <t>Verify product stock limits block checkout excess items</t>
+  </si>
+  <si>
+    <t>WEB-TC-169</t>
+  </si>
+  <si>
+    <t>Verify remove multiple items clears cart completely</t>
+  </si>
+  <si>
+    <t>WEB-TC-170</t>
+  </si>
+  <si>
+    <t>Verify custom note input field for seller delivery details</t>
+  </si>
+  <si>
+    <t>WEB-TC-171</t>
+  </si>
+  <si>
+    <t>Verify cart items loading animation skeleton widgets</t>
+  </si>
+  <si>
+    <t>WEB-TC-172</t>
+  </si>
+  <si>
+    <t>Verify cart layout maintains design on mobile ports</t>
+  </si>
+  <si>
+    <t>WEB-TC-173</t>
+  </si>
+  <si>
+    <t>Verify promo coupon input text box is visible</t>
+  </si>
+  <si>
+    <t>WEB-TC-174</t>
+  </si>
+  <si>
+    <t>Verify applying invalid promo coupon alerts error</t>
+  </si>
+  <si>
+    <t>WEB-TC-175</t>
+  </si>
+  <si>
+    <t>Verify correct calculation when promo coupon applies successfully</t>
+  </si>
+  <si>
+    <t>WEB-TC-176</t>
+  </si>
+  <si>
+    <t>Checkout Screen</t>
+  </si>
+  <si>
+    <t>Verify checkout items summary list maps cart items</t>
+  </si>
+  <si>
+    <t>WEB-TC-177</t>
+  </si>
+  <si>
+    <t>Verify billing details form input names fields</t>
+  </si>
+  <si>
+    <t>WEB-TC-178</t>
+  </si>
+  <si>
+    <t>Verify billing details validation checks on empty fields</t>
+  </si>
+  <si>
+    <t>WEB-TC-179</t>
+  </si>
+  <si>
+    <t>Verify billing details email format regex matches</t>
+  </si>
+  <si>
+    <t>WEB-TC-180</t>
+  </si>
+  <si>
+    <t>Verify billing details phone number length restrictions</t>
+  </si>
+  <si>
+    <t>WEB-TC-181</t>
+  </si>
+  <si>
+    <t>Verify delivery hostel room select dropdown options</t>
+  </si>
+  <si>
+    <t>WEB-TC-182</t>
+  </si>
+  <si>
+    <t>Verify cash on delivery radio selector is checked by default</t>
+  </si>
+  <si>
+    <t>WEB-TC-183</t>
+  </si>
+  <si>
+    <t>Verify credit debit card online payment options accordion</t>
+  </si>
+  <si>
+    <t>WEB-TC-184</t>
+  </si>
+  <si>
+    <t>Verify card details input format validators (Luhn formula)</t>
+  </si>
+  <si>
+    <t>WEB-TC-185</t>
+  </si>
+  <si>
+    <t>Verify card CVV field number format checks length</t>
+  </si>
+  <si>
+    <t>WEB-TC-186</t>
+  </si>
+  <si>
+    <t>Verify card expiry date format placeholder MM YY validation</t>
+  </si>
+  <si>
+    <t>WEB-TC-187</t>
+  </si>
+  <si>
+    <t>Verify place order submit button starts API request</t>
+  </si>
+  <si>
+    <t>WEB-TC-188</t>
+  </si>
+  <si>
+    <t>Verify loading overlay prevents duplicate submit double clicks</t>
+  </si>
+  <si>
+    <t>WEB-TC-189</t>
+  </si>
+  <si>
+    <t>Verify checkout fails if item goes out of stock in backend</t>
+  </si>
+  <si>
+    <t>WEB-TC-190</t>
+  </si>
+  <si>
+    <t>Verify checkout success updates user orders database records</t>
+  </si>
+  <si>
+    <t>WEB-TC-191</t>
+  </si>
+  <si>
+    <t>Verify redirect route to order success page details</t>
+  </si>
+  <si>
+    <t>WEB-TC-192</t>
+  </si>
+  <si>
+    <t>Verify order success screen displays order confirmation number ID</t>
+  </si>
+  <si>
+    <t>WEB-TC-193</t>
+  </si>
+  <si>
+    <t>Verify order invoice download PDF button exists</t>
+  </si>
+  <si>
+    <t>WEB-TC-194</t>
+  </si>
+  <si>
+    <t>Verify email confirmation receipt dispatch call</t>
+  </si>
+  <si>
+    <t>WEB-TC-195</t>
+  </si>
+  <si>
+    <t>Verify checkout route guest access redirect guard</t>
+  </si>
+  <si>
+    <t>WEB-TC-196</t>
+  </si>
+  <si>
+    <t>Verify checkout session cancels on close navigates back</t>
+  </si>
+  <si>
+    <t>WEB-TC-197</t>
+  </si>
+  <si>
+    <t>Verify pricing matches cart total values exactly</t>
+  </si>
+  <si>
+    <t>WEB-TC-198</t>
+  </si>
+  <si>
+    <t>Verify input security prevention checks against SQL injection</t>
+  </si>
+  <si>
+    <t>WEB-TC-199</t>
+  </si>
+  <si>
+    <t>Verify billing info retains values on validation reload errors</t>
+  </si>
+  <si>
+    <t>WEB-TC-200</t>
+  </si>
+  <si>
+    <t>Verify checkout page design layout scales on screens</t>
+  </si>
+  <si>
+    <t>WEB-TC-201</t>
+  </si>
+  <si>
+    <t>Listing Creation Screen</t>
+  </si>
+  <si>
+    <t>Verify product title input element exists</t>
+  </si>
+  <si>
+    <t>WEB-TC-202</t>
+  </si>
+  <si>
+    <t>Verify price field input number validation constraints</t>
+  </si>
+  <si>
+    <t>WEB-TC-203</t>
+  </si>
+  <si>
+    <t>Verify category select element options</t>
+  </si>
+  <si>
+    <t>WEB-TC-204</t>
+  </si>
+  <si>
+    <t>Verify condition select element options</t>
+  </si>
+  <si>
+    <t>WEB-TC-205</t>
+  </si>
+  <si>
+    <t>Verify product description text area input constraints</t>
+  </si>
+  <si>
+    <t>WEB-TC-206</t>
+  </si>
+  <si>
+    <t>Verify drag and drop file upload region display</t>
+  </si>
+  <si>
+    <t>WEB-TC-207</t>
+  </si>
+  <si>
+    <t>Verify file input accepts multiple images files</t>
+  </si>
+  <si>
+    <t>WEB-TC-208</t>
+  </si>
+  <si>
+    <t>Verify image file size limits validation checks (max 5MB)</t>
+  </si>
+  <si>
+    <t>WEB-TC-209</t>
+  </si>
+  <si>
+    <t>Verify image format validation allows JPEG PNG WEBP</t>
+  </si>
+  <si>
+    <t>WEB-TC-210</t>
+  </si>
+  <si>
+    <t>Verify non-image formats are rejected</t>
+  </si>
+  <si>
+    <t>WEB-TC-211</t>
+  </si>
+  <si>
+    <t>Verify image thumbnails preview display inside list</t>
+  </si>
+  <si>
+    <t>WEB-TC-212</t>
+  </si>
+  <si>
+    <t>Verify remove thumbnail preview button action</t>
+  </si>
+  <si>
+    <t>WEB-TC-213</t>
+  </si>
+  <si>
+    <t>Verify product title length validations (min 5 characters)</t>
+  </si>
+  <si>
+    <t>WEB-TC-214</t>
+  </si>
+  <si>
+    <t>Verify price limits block negative values inputs</t>
+  </si>
+  <si>
+    <t>WEB-TC-215</t>
+  </si>
+  <si>
+    <t>Verify character countdown counter updates dynamically</t>
+  </si>
+  <si>
+    <t>WEB-TC-216</t>
+  </si>
+  <si>
+    <t>Verify list product submit button launches API calls</t>
+  </si>
+  <si>
+    <t>WEB-TC-217</t>
+  </si>
+  <si>
+    <t>Verify progress indicator bar updates on file upload</t>
+  </si>
+  <si>
+    <t>WEB-TC-218</t>
+  </si>
+  <si>
+    <t>Verify listing validation prevents blank fields submits</t>
+  </si>
+  <si>
+    <t>WEB-TC-219</t>
+  </si>
+  <si>
+    <t>Verify listing creation success alert popups notification</t>
+  </si>
+  <si>
+    <t>WEB-TC-220</t>
+  </si>
+  <si>
+    <t>Verify redirect to user dashboard listings feed on success</t>
+  </si>
+  <si>
+    <t>WEB-TC-221</t>
+  </si>
+  <si>
+    <t>Verify route guard prevents guest listings posting</t>
+  </si>
+  <si>
+    <t>WEB-TC-222</t>
+  </si>
+  <si>
+    <t>Verify route guard redirects unverified accounts to verification</t>
+  </si>
+  <si>
+    <t>WEB-TC-223</t>
+  </si>
+  <si>
+    <t>Verify location default set to user campus tag info</t>
+  </si>
+  <si>
+    <t>WEB-TC-224</t>
+  </si>
+  <si>
+    <t>Verify create listings page design layout responsiveness</t>
+  </si>
+  <si>
+    <t>WEB-TC-225</t>
+  </si>
+  <si>
+    <t>Verify draft saving status updates in background</t>
+  </si>
+  <si>
+    <t>WEB-TC-226</t>
+  </si>
+  <si>
+    <t>User Dashboard</t>
+  </si>
+  <si>
+    <t>Verify customer dashboard sidebar menu links</t>
+  </si>
+  <si>
+    <t>WEB-TC-227</t>
+  </si>
+  <si>
+    <t>Verify dashboard displays current user email welcome</t>
+  </si>
+  <si>
+    <t>WEB-TC-228</t>
+  </si>
+  <si>
+    <t>Verify user statistics summary cards data totals</t>
+  </si>
+  <si>
+    <t>WEB-TC-229</t>
+  </si>
+  <si>
+    <t>Verify customer my active listings data feed</t>
+  </si>
+  <si>
+    <t>WEB-TC-230</t>
+  </si>
+  <si>
+    <t>Verify edit product details modal opens from listings</t>
+  </si>
+  <si>
+    <t>WEB-TC-231</t>
+  </si>
+  <si>
+    <t>Verify update listing details submits API modifications</t>
+  </si>
+  <si>
+    <t>WEB-TC-232</t>
+  </si>
+  <si>
+    <t>Verify delete listing action prompts confirm dialog</t>
+  </si>
+  <si>
+    <t>WEB-TC-233</t>
+  </si>
+  <si>
+    <t>Verify confirm delete listing cleans DB records</t>
+  </si>
+  <si>
+    <t>WEB-TC-234</t>
+  </si>
+  <si>
+    <t>Verify marking item sold updates availability status</t>
+  </si>
+  <si>
+    <t>WEB-TC-235</t>
+  </si>
+  <si>
+    <t>Verify user saved wishlist items collection feed</t>
+  </si>
+  <si>
+    <t>WEB-TC-236</t>
+  </si>
+  <si>
+    <t>Verify remove item from saved list updates dashboard</t>
+  </si>
+  <si>
+    <t>WEB-TC-237</t>
+  </si>
+  <si>
+    <t>Verify user purchases history list grid display</t>
+  </si>
+  <si>
+    <t>WEB-TC-238</t>
+  </si>
+  <si>
+    <t>Verify purchase details page view navigation</t>
+  </si>
+  <si>
+    <t>WEB-TC-239</t>
+  </si>
+  <si>
+    <t>Verify user sales orders dashboard tab</t>
+  </si>
+  <si>
+    <t>WEB-TC-240</t>
+  </si>
+  <si>
+    <t>Verify edit profile information inputs values</t>
+  </si>
+  <si>
+    <t>WEB-TC-241</t>
+  </si>
+  <si>
+    <t>Verify update profile details saves to database</t>
+  </si>
+  <si>
+    <t>WEB-TC-242</t>
+  </si>
+  <si>
+    <t>Verify upload custom profile picture avatar image</t>
+  </si>
+  <si>
+    <t>WEB-TC-243</t>
+  </si>
+  <si>
+    <t>Verify validation errors on profile inputs</t>
+  </si>
+  <si>
+    <t>WEB-TC-244</t>
+  </si>
+  <si>
+    <t>Verify change account password inputs constraints</t>
+  </si>
+  <si>
+    <t>WEB-TC-245</t>
+  </si>
+  <si>
+    <t>Verify update password submits API verification check</t>
+  </si>
+  <si>
+    <t>WEB-TC-246</t>
+  </si>
+  <si>
+    <t>Verify email notifications settings toggles switch</t>
+  </si>
+  <si>
+    <t>WEB-TC-247</t>
+  </si>
+  <si>
+    <t>Verify dark theme mode styling changes on dashboard</t>
+  </si>
+  <si>
+    <t>WEB-TC-248</t>
+  </si>
+  <si>
+    <t>Verify dashboard route guard guest access redirect</t>
+  </si>
+  <si>
+    <t>WEB-TC-249</t>
+  </si>
+  <si>
+    <t>Verify responsive menu button on mobile dashboards</t>
+  </si>
+  <si>
+    <t>WEB-TC-250</t>
+  </si>
+  <si>
+    <t>Verify customer session sign out invalidation</t>
+  </si>
+  <si>
+    <t>WEB-TC-251</t>
+  </si>
+  <si>
+    <t>Admin Dashboard</t>
+  </si>
+  <si>
+    <t>Verify admin dashboard sidebar layout links</t>
+  </si>
+  <si>
+    <t>WEB-TC-252</t>
+  </si>
+  <si>
+    <t>Verify admin statistics widgets map totals</t>
+  </si>
+  <si>
+    <t>WEB-TC-253</t>
+  </si>
+  <si>
+    <t>Verify users registration analytics graphs render</t>
+  </si>
+  <si>
+    <t>WEB-TC-254</t>
+  </si>
+  <si>
+    <t>Verify pending listings approval stream queue feed</t>
+  </si>
+  <si>
+    <t>WEB-TC-255</t>
+  </si>
+  <si>
+    <t>Verify admin view pending listing detail modal view</t>
+  </si>
+  <si>
+    <t>WEB-TC-256</t>
+  </si>
+  <si>
+    <t>Verify admin approve listing button confirms status</t>
+  </si>
+  <si>
+    <t>WEB-TC-257</t>
+  </si>
+  <si>
+    <t>Verify approved listing displays on public marketplace</t>
+  </si>
+  <si>
+    <t>WEB-TC-258</t>
+  </si>
+  <si>
+    <t>Verify admin reject listing reason text area popup</t>
+  </si>
+  <si>
+    <t>WEB-TC-259</t>
+  </si>
+  <si>
+    <t>Verify reject listing updates status database records</t>
+  </si>
+  <si>
+    <t>WEB-TC-260</t>
+  </si>
+  <si>
+    <t>Verify users management directory grid data table</t>
+  </si>
+  <si>
+    <t>WEB-TC-261</t>
+  </si>
+  <si>
+    <t>Verify search users search bar filter list</t>
+  </si>
+  <si>
+    <t>WEB-TC-262</t>
+  </si>
+  <si>
+    <t>Verify edit user details admin modal values</t>
+  </si>
+  <si>
+    <t>WEB-TC-263</t>
+  </si>
+  <si>
+    <t>Verify user verification tag status toggle switches</t>
+  </si>
+  <si>
+    <t>WEB-TC-264</t>
+  </si>
+  <si>
+    <t>Verify admin block deactivate malicious user profile</t>
+  </si>
+  <si>
+    <t>WEB-TC-265</t>
+  </si>
+  <si>
+    <t>Verify deactivated account cannot pass login check</t>
+  </si>
+  <si>
+    <t>WEB-TC-266</t>
+  </si>
+  <si>
+    <t>Verify flagged product reports feed panel list</t>
+  </si>
+  <si>
+    <t>WEB-TC-267</t>
+  </si>
+  <si>
+    <t>Verify admin dismiss flagged report action click</t>
+  </si>
+  <si>
+    <t>WEB-TC-268</t>
+  </si>
+  <si>
+    <t>Verify admin delete flagged listing action</t>
+  </si>
+  <si>
+    <t>WEB-TC-269</t>
+  </si>
+  <si>
+    <t>Verify platform settings parameter edit configuration</t>
+  </si>
+  <si>
+    <t>WEB-TC-270</t>
+  </si>
+  <si>
+    <t>Verify admin profile details edit panels</t>
+  </si>
+  <si>
+    <t>WEB-TC-271</t>
+  </si>
+  <si>
+    <t>Verify system logs stream view panels content</t>
+  </si>
+  <si>
+    <t>WEB-TC-272</t>
+  </si>
+  <si>
+    <t>Verify admin routing guard blocks general users</t>
+  </si>
+  <si>
+    <t>WEB-TC-273</t>
+  </si>
+  <si>
+    <t>Verify admin route guard redirects guest sessions</t>
+  </si>
+  <si>
+    <t>WEB-TC-274</t>
+  </si>
+  <si>
+    <t>Verify responsive admin views layout styles</t>
+  </si>
+  <si>
+    <t>WEB-TC-275</t>
+  </si>
+  <si>
+    <t>Verify admin sign out destroys JWT credentials</t>
+  </si>
+  <si>
+    <t>WEB-TC-276</t>
+  </si>
+  <si>
+    <t>Chat Screen</t>
+  </si>
+  <si>
+    <t>Verify chat inbox layout splits conversations and feed</t>
+  </si>
+  <si>
+    <t>WEB-TC-277</t>
+  </si>
+  <si>
+    <t>Verify chat sidebar populates list of active contacts</t>
+  </si>
+  <si>
+    <t>WEB-TC-278</t>
+  </si>
+  <si>
+    <t>Verify message history feed displays previous logs</t>
+  </si>
+  <si>
+    <t>WEB-TC-279</t>
+  </si>
+  <si>
+    <t>Verify contacts status online offline tag labels</t>
+  </si>
+  <si>
+    <t>WEB-TC-280</t>
+  </si>
+  <si>
+    <t>Verify click contact opens active thread conversation</t>
+  </si>
+  <si>
+    <t>WEB-TC-281</t>
+  </si>
+  <si>
+    <t>Verify message text input field is active</t>
+  </si>
+  <si>
+    <t>WEB-TC-282</t>
+  </si>
+  <si>
+    <t>Verify send message button triggers socket dispatch</t>
+  </si>
+  <si>
+    <t>WEB-TC-283</t>
+  </si>
+  <si>
+    <t>Verify message bubbles distinguish sender vs receiver</t>
+  </si>
+  <si>
+    <t>WEB-TC-284</t>
+  </si>
+  <si>
+    <t>Verify socket connection joins room identifier rooms</t>
+  </si>
+  <si>
+    <t>WEB-TC-285</t>
+  </si>
+  <si>
+    <t>Verify sent messages appear instantly in chat feed</t>
+  </si>
+  <si>
+    <t>WEB-TC-286</t>
+  </si>
+  <si>
+    <t>Verify message timestamps display next to bubbles</t>
+  </si>
+  <si>
+    <t>WEB-TC-287</t>
+  </si>
+  <si>
+    <t>Verify input handles multiline messages on shift-enter</t>
+  </si>
+  <si>
+    <t>WEB-TC-288</t>
+  </si>
+  <si>
+    <t>Verify empty message input blocks send buttons clicks</t>
+  </si>
+  <si>
+    <t>WEB-TC-289</t>
+  </si>
+  <si>
+    <t>Verify message notification toaster displays on dashboard</t>
+  </si>
+  <si>
+    <t>WEB-TC-290</t>
+  </si>
+  <si>
+    <t>Verify badge alert counter updates on inbox menu links</t>
+  </si>
+  <si>
+    <t>WEB-TC-291</t>
+  </si>
+  <si>
+    <t>Verify support contact form fields details inputs</t>
+  </si>
+  <si>
+    <t>WEB-TC-292</t>
+  </si>
+  <si>
+    <t>Verify support contact submission sends ticket email</t>
+  </si>
+  <si>
+    <t>WEB-TC-293</t>
+  </si>
+  <si>
+    <t>Verify support contact success feedback notification status</t>
+  </si>
+  <si>
+    <t>WEB-TC-294</t>
+  </si>
+  <si>
+    <t>Verify collapsible FAQ accordion headers click</t>
+  </si>
+  <si>
+    <t>WEB-TC-295</t>
+  </si>
+  <si>
+    <t>Verify FAQ descriptions display on headers expansion</t>
+  </si>
+  <si>
+    <t>WEB-TC-296</t>
+  </si>
+  <si>
+    <t>Verify help center query search filter input</t>
+  </si>
+  <si>
+    <t>WEB-TC-297</t>
+  </si>
+  <si>
+    <t>Verify chat layouts scaling matches mobile formats</t>
+  </si>
+  <si>
+    <t>WEB-TC-298</t>
+  </si>
+  <si>
+    <t>Verify security filter checks message text for XSS script injection</t>
+  </si>
+  <si>
+    <t>WEB-TC-299</t>
+  </si>
+  <si>
+    <t>Verify media attachments options menu displays</t>
+  </si>
+  <si>
+    <t>WEB-TC-300</t>
+  </si>
+  <si>
+    <t>Verify chat notifications settings panel load</t>
   </si>
 </sst>
 </file>
@@ -1467,7 +2499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G307"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1511,10 +2543,10 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="B5" s="5">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="C5" s="6">
         <v>0</v>
@@ -1574,16 +2606,16 @@
         <v>21</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="D9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>23</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>24</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>19</v>
@@ -1594,19 +2626,19 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="D10" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>26</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>28</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>19</v>
@@ -1617,19 +2649,19 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>29</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>32</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>19</v>
@@ -1640,19 +2672,19 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>19</v>
@@ -1663,19 +2695,19 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>19</v>
@@ -1686,19 +2718,19 @@
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>19</v>
@@ -1709,19 +2741,19 @@
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>19</v>
@@ -1732,19 +2764,19 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>19</v>
@@ -1755,19 +2787,19 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>19</v>
@@ -1778,19 +2810,19 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>19</v>
@@ -1801,19 +2833,19 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>19</v>
@@ -1824,19 +2856,19 @@
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>19</v>
@@ -1847,19 +2879,19 @@
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="F21" s="12" t="s">
         <v>19</v>
@@ -1870,19 +2902,19 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>19</v>
@@ -1893,19 +2925,19 @@
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>19</v>
@@ -1916,19 +2948,19 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>19</v>
@@ -1939,19 +2971,19 @@
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>19</v>
@@ -1962,19 +2994,19 @@
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="F26" s="10" t="s">
         <v>19</v>
@@ -1985,19 +3017,19 @@
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>19</v>
@@ -2008,19 +3040,19 @@
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="F28" s="10" t="s">
         <v>19</v>
@@ -2031,19 +3063,19 @@
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>19</v>
@@ -2054,19 +3086,19 @@
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>19</v>
@@ -2077,19 +3109,19 @@
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="F31" s="12" t="s">
         <v>19</v>
@@ -2100,19 +3132,19 @@
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>19</v>
@@ -2123,19 +3155,19 @@
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="F33" s="12" t="s">
         <v>19</v>
@@ -2146,19 +3178,19 @@
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="F34" s="10" t="s">
         <v>19</v>
@@ -2169,19 +3201,19 @@
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="F35" s="12" t="s">
         <v>19</v>
@@ -2192,19 +3224,19 @@
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="F36" s="10" t="s">
         <v>19</v>
@@ -2215,19 +3247,19 @@
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="F37" s="12" t="s">
         <v>19</v>
@@ -2238,19 +3270,19 @@
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="F38" s="10" t="s">
         <v>19</v>
@@ -2261,19 +3293,19 @@
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="F39" s="12" t="s">
         <v>19</v>
@@ -2284,19 +3316,19 @@
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="D40" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="F40" s="10" t="s">
         <v>19</v>
@@ -2307,19 +3339,19 @@
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>19</v>
@@ -2330,19 +3362,19 @@
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>127</v>
+        <v>49</v>
       </c>
       <c r="F42" s="10" t="s">
         <v>19</v>
@@ -2353,19 +3385,19 @@
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="F43" s="12" t="s">
         <v>19</v>
@@ -2376,19 +3408,19 @@
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="F44" s="10" t="s">
         <v>19</v>
@@ -2399,19 +3431,19 @@
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="F45" s="12" t="s">
         <v>19</v>
@@ -2422,19 +3454,19 @@
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="F46" s="10" t="s">
         <v>19</v>
@@ -2445,19 +3477,19 @@
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="F47" s="12" t="s">
         <v>19</v>
@@ -2468,19 +3500,19 @@
     </row>
     <row r="48" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="F48" s="10" t="s">
         <v>19</v>
@@ -2491,19 +3523,19 @@
     </row>
     <row r="49" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>148</v>
+        <v>72</v>
       </c>
       <c r="F49" s="12" t="s">
         <v>19</v>
@@ -2514,19 +3546,19 @@
     </row>
     <row r="50" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="D50" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>151</v>
+        <v>49</v>
       </c>
       <c r="F50" s="10" t="s">
         <v>19</v>
@@ -2537,19 +3569,19 @@
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="D51" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="F51" s="12" t="s">
         <v>19</v>
@@ -2560,19 +3592,19 @@
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="D52" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>157</v>
+        <v>49</v>
       </c>
       <c r="F52" s="10" t="s">
         <v>19</v>
@@ -2583,19 +3615,19 @@
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="D53" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="F53" s="12" t="s">
         <v>19</v>
@@ -2606,19 +3638,19 @@
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="D54" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="F54" s="10" t="s">
         <v>19</v>
@@ -2629,19 +3661,19 @@
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="D55" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="F55" s="12" t="s">
         <v>19</v>
@@ -2652,19 +3684,19 @@
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="D56" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="F56" s="10" t="s">
         <v>19</v>
@@ -2675,19 +3707,19 @@
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="D57" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F57" s="12" t="s">
         <v>19</v>
@@ -2698,19 +3730,19 @@
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="F58" s="10" t="s">
         <v>19</v>
@@ -2721,19 +3753,19 @@
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="D59" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="F59" s="12" t="s">
         <v>19</v>
@@ -2744,19 +3776,19 @@
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>30</v>
+        <v>143</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="D60" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>180</v>
+        <v>49</v>
       </c>
       <c r="F60" s="10" t="s">
         <v>19</v>
@@ -2767,19 +3799,19 @@
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="D61" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>183</v>
+        <v>49</v>
       </c>
       <c r="F61" s="12" t="s">
         <v>19</v>
@@ -2790,19 +3822,19 @@
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="D62" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>186</v>
+        <v>49</v>
       </c>
       <c r="F62" s="10" t="s">
         <v>19</v>
@@ -2813,19 +3845,19 @@
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>188</v>
+        <v>155</v>
       </c>
       <c r="D63" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>189</v>
+        <v>72</v>
       </c>
       <c r="F63" s="12" t="s">
         <v>19</v>
@@ -2836,19 +3868,19 @@
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>15</v>
+        <v>143</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>191</v>
+        <v>157</v>
       </c>
       <c r="D64" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>192</v>
+        <v>49</v>
       </c>
       <c r="F64" s="10" t="s">
         <v>19</v>
@@ -2859,19 +3891,19 @@
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="D65" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>195</v>
+        <v>49</v>
       </c>
       <c r="F65" s="12" t="s">
         <v>19</v>
@@ -2882,19 +3914,19 @@
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>196</v>
+        <v>160</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>197</v>
+        <v>161</v>
       </c>
       <c r="D66" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>198</v>
+        <v>65</v>
       </c>
       <c r="F66" s="10" t="s">
         <v>19</v>
@@ -2905,19 +3937,19 @@
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>30</v>
+        <v>143</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>200</v>
+        <v>163</v>
       </c>
       <c r="D67" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>201</v>
+        <v>65</v>
       </c>
       <c r="F67" s="12" t="s">
         <v>19</v>
@@ -2928,19 +3960,19 @@
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="D68" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="F68" s="10" t="s">
         <v>19</v>
@@ -2951,19 +3983,19 @@
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
-        <v>205</v>
+        <v>166</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>206</v>
+        <v>167</v>
       </c>
       <c r="D69" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>207</v>
+        <v>65</v>
       </c>
       <c r="F69" s="12" t="s">
         <v>19</v>
@@ -2974,19 +4006,19 @@
     </row>
     <row r="70" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>209</v>
+        <v>169</v>
       </c>
       <c r="D70" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>210</v>
+        <v>62</v>
       </c>
       <c r="F70" s="10" t="s">
         <v>19</v>
@@ -2997,19 +4029,19 @@
     </row>
     <row r="71" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>15</v>
+        <v>143</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>212</v>
+        <v>171</v>
       </c>
       <c r="D71" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>213</v>
+        <v>49</v>
       </c>
       <c r="F71" s="12" t="s">
         <v>19</v>
@@ -3020,19 +4052,19 @@
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>214</v>
+        <v>172</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="D72" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="F72" s="10" t="s">
         <v>19</v>
@@ -3043,19 +4075,19 @@
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>217</v>
+        <v>174</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>218</v>
+        <v>175</v>
       </c>
       <c r="D73" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>219</v>
+        <v>49</v>
       </c>
       <c r="F73" s="12" t="s">
         <v>19</v>
@@ -3066,19 +4098,19 @@
     </row>
     <row r="74" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>220</v>
+        <v>176</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>30</v>
+        <v>143</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>221</v>
+        <v>177</v>
       </c>
       <c r="D74" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>222</v>
+        <v>65</v>
       </c>
       <c r="F74" s="10" t="s">
         <v>19</v>
@@ -3089,19 +4121,19 @@
     </row>
     <row r="75" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>223</v>
+        <v>178</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="D75" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>225</v>
+        <v>65</v>
       </c>
       <c r="F75" s="12" t="s">
         <v>19</v>
@@ -3112,19 +4144,19 @@
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>226</v>
+        <v>180</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>227</v>
+        <v>181</v>
       </c>
       <c r="D76" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>228</v>
+        <v>65</v>
       </c>
       <c r="F76" s="10" t="s">
         <v>19</v>
@@ -3135,19 +4167,19 @@
     </row>
     <row r="77" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>229</v>
+        <v>182</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>230</v>
+        <v>183</v>
       </c>
       <c r="D77" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>231</v>
+        <v>49</v>
       </c>
       <c r="F77" s="12" t="s">
         <v>19</v>
@@ -3158,19 +4190,19 @@
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
-        <v>232</v>
+        <v>184</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>15</v>
+        <v>143</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>233</v>
+        <v>185</v>
       </c>
       <c r="D78" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>148</v>
+        <v>49</v>
       </c>
       <c r="F78" s="10" t="s">
         <v>19</v>
@@ -3181,19 +4213,19 @@
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
-        <v>234</v>
+        <v>186</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>235</v>
+        <v>187</v>
       </c>
       <c r="D79" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>236</v>
+        <v>65</v>
       </c>
       <c r="F79" s="12" t="s">
         <v>19</v>
@@ -3204,19 +4236,19 @@
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
-        <v>237</v>
+        <v>188</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>238</v>
+        <v>189</v>
       </c>
       <c r="D80" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>239</v>
+        <v>49</v>
       </c>
       <c r="F80" s="10" t="s">
         <v>19</v>
@@ -3227,19 +4259,19 @@
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>30</v>
+        <v>143</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>241</v>
+        <v>191</v>
       </c>
       <c r="D81" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="F81" s="12" t="s">
         <v>19</v>
@@ -3250,19 +4282,19 @@
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
-        <v>242</v>
+        <v>192</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>243</v>
+        <v>193</v>
       </c>
       <c r="D82" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>244</v>
+        <v>49</v>
       </c>
       <c r="F82" s="10" t="s">
         <v>19</v>
@@ -3273,19 +4305,19 @@
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>245</v>
+        <v>194</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>246</v>
+        <v>196</v>
       </c>
       <c r="D83" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>119</v>
+        <v>197</v>
       </c>
       <c r="F83" s="12" t="s">
         <v>19</v>
@@ -3296,19 +4328,19 @@
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
-        <v>247</v>
+        <v>198</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>42</v>
+        <v>195</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>248</v>
+        <v>199</v>
       </c>
       <c r="D84" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>249</v>
+        <v>200</v>
       </c>
       <c r="F84" s="10" t="s">
         <v>19</v>
@@ -3319,19 +4351,19 @@
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>250</v>
+        <v>201</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>15</v>
+        <v>195</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>251</v>
+        <v>202</v>
       </c>
       <c r="D85" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>252</v>
+        <v>203</v>
       </c>
       <c r="F85" s="12" t="s">
         <v>19</v>
@@ -3342,19 +4374,19 @@
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
-        <v>253</v>
+        <v>204</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>22</v>
+        <v>195</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="D86" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="F86" s="10" t="s">
         <v>19</v>
@@ -3365,19 +4397,19 @@
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>256</v>
+        <v>206</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>26</v>
+        <v>195</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>257</v>
+        <v>207</v>
       </c>
       <c r="D87" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>258</v>
+        <v>203</v>
       </c>
       <c r="F87" s="12" t="s">
         <v>19</v>
@@ -3388,19 +4420,19 @@
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>259</v>
+        <v>208</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>30</v>
+        <v>195</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="D88" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="F88" s="10" t="s">
         <v>19</v>
@@ -3411,19 +4443,19 @@
     </row>
     <row r="89" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>262</v>
+        <v>210</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>263</v>
+        <v>211</v>
       </c>
       <c r="D89" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>264</v>
+        <v>212</v>
       </c>
       <c r="F89" s="12" t="s">
         <v>19</v>
@@ -3434,19 +4466,19 @@
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>266</v>
+        <v>214</v>
       </c>
       <c r="D90" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>267</v>
+        <v>203</v>
       </c>
       <c r="F90" s="10" t="s">
         <v>19</v>
@@ -3457,19 +4489,19 @@
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>42</v>
+        <v>195</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>269</v>
+        <v>216</v>
       </c>
       <c r="D91" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="F91" s="12" t="s">
         <v>19</v>
@@ -3480,19 +4512,19 @@
     </row>
     <row r="92" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
-        <v>271</v>
+        <v>217</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>15</v>
+        <v>195</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>272</v>
+        <v>218</v>
       </c>
       <c r="D92" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>154</v>
+        <v>219</v>
       </c>
       <c r="F92" s="10" t="s">
         <v>19</v>
@@ -3503,19 +4535,19 @@
     </row>
     <row r="93" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
-        <v>273</v>
+        <v>220</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>22</v>
+        <v>195</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>274</v>
+        <v>221</v>
       </c>
       <c r="D93" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>275</v>
+        <v>222</v>
       </c>
       <c r="F93" s="12" t="s">
         <v>19</v>
@@ -3526,19 +4558,19 @@
     </row>
     <row r="94" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
-        <v>276</v>
+        <v>223</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>26</v>
+        <v>195</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="D94" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>278</v>
+        <v>197</v>
       </c>
       <c r="F94" s="10" t="s">
         <v>19</v>
@@ -3549,19 +4581,19 @@
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
-        <v>279</v>
+        <v>225</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>30</v>
+        <v>195</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>280</v>
+        <v>226</v>
       </c>
       <c r="D95" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>281</v>
+        <v>203</v>
       </c>
       <c r="F95" s="12" t="s">
         <v>19</v>
@@ -3572,19 +4604,19 @@
     </row>
     <row r="96" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
-        <v>282</v>
+        <v>227</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>283</v>
+        <v>228</v>
       </c>
       <c r="D96" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>284</v>
+        <v>212</v>
       </c>
       <c r="F96" s="10" t="s">
         <v>19</v>
@@ -3595,19 +4627,19 @@
     </row>
     <row r="97" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
-        <v>285</v>
+        <v>229</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>286</v>
+        <v>230</v>
       </c>
       <c r="D97" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>287</v>
+        <v>200</v>
       </c>
       <c r="F97" s="12" t="s">
         <v>19</v>
@@ -3618,19 +4650,19 @@
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
-        <v>288</v>
+        <v>231</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>42</v>
+        <v>195</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>289</v>
+        <v>232</v>
       </c>
       <c r="D98" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>290</v>
+        <v>203</v>
       </c>
       <c r="F98" s="10" t="s">
         <v>19</v>
@@ -3641,19 +4673,19 @@
     </row>
     <row r="99" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
-        <v>291</v>
+        <v>233</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>15</v>
+        <v>195</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>292</v>
+        <v>234</v>
       </c>
       <c r="D99" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>293</v>
+        <v>235</v>
       </c>
       <c r="F99" s="12" t="s">
         <v>19</v>
@@ -3664,19 +4696,19 @@
     </row>
     <row r="100" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="10" t="s">
-        <v>294</v>
+        <v>236</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>22</v>
+        <v>195</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>295</v>
+        <v>237</v>
       </c>
       <c r="D100" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>296</v>
+        <v>203</v>
       </c>
       <c r="F100" s="10" t="s">
         <v>19</v>
@@ -3687,19 +4719,19 @@
     </row>
     <row r="101" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
-        <v>297</v>
+        <v>238</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>26</v>
+        <v>195</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>298</v>
+        <v>239</v>
       </c>
       <c r="D101" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>299</v>
+        <v>200</v>
       </c>
       <c r="F101" s="12" t="s">
         <v>19</v>
@@ -3710,19 +4742,19 @@
     </row>
     <row r="102" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>30</v>
+        <v>195</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>301</v>
+        <v>241</v>
       </c>
       <c r="D102" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>302</v>
+        <v>200</v>
       </c>
       <c r="F102" s="10" t="s">
         <v>19</v>
@@ -3733,19 +4765,19 @@
     </row>
     <row r="103" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
-        <v>303</v>
+        <v>242</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>304</v>
+        <v>243</v>
       </c>
       <c r="D103" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>305</v>
+        <v>200</v>
       </c>
       <c r="F103" s="12" t="s">
         <v>19</v>
@@ -3756,19 +4788,19 @@
     </row>
     <row r="104" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
-        <v>306</v>
+        <v>244</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D104" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>308</v>
+        <v>200</v>
       </c>
       <c r="F104" s="10" t="s">
         <v>19</v>
@@ -3779,19 +4811,19 @@
     </row>
     <row r="105" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
-        <v>309</v>
+        <v>246</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>42</v>
+        <v>195</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>310</v>
+        <v>247</v>
       </c>
       <c r="D105" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E105" s="12" t="s">
-        <v>311</v>
+        <v>197</v>
       </c>
       <c r="F105" s="12" t="s">
         <v>19</v>
@@ -3802,19 +4834,19 @@
     </row>
     <row r="106" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
-        <v>312</v>
+        <v>248</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>15</v>
+        <v>195</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>313</v>
+        <v>249</v>
       </c>
       <c r="D106" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>314</v>
+        <v>219</v>
       </c>
       <c r="F106" s="10" t="s">
         <v>19</v>
@@ -3825,24 +4857,4624 @@
     </row>
     <row r="107" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="B107" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="D107" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E107" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="F107" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G107" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="B108" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="D108" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="F108" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G108" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="109" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="B109" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="D109" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E109" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F109" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G109" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="110" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="B110" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C110" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="D110" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F110" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G110" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="B111" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E111" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="F111" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G111" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="B112" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C112" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F112" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G112" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="113" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="D113" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E113" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="F113" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G113" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="D114" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F114" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G114" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="115" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="B115" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E115" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F115" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G115" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="B116" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F116" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G116" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="117" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="B117" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E117" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F117" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G117" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="118" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="B118" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C118" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F118" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G118" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="119" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="B119" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E119" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F119" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G119" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="120" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="B120" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F120" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G120" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="121" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="B121" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E121" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F121" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G121" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="122" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="B122" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C122" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E122" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F122" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G122" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="123" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="B123" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C123" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="D123" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E123" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F123" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G123" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="124" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="B124" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C124" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="D124" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F124" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G124" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="125" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="B125" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C125" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="D125" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E125" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F125" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G125" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="126" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="B126" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C126" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="D126" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F126" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G126" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="127" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="B127" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C127" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E127" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F127" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G127" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="128" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="B128" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C128" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="D128" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E128" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F128" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G128" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="129" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="B129" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="D129" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E129" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F129" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G129" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="130" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="B130" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C130" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="D130" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E130" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F130" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G130" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="131" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B131" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="D131" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E131" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F131" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G131" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="132" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="B132" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C132" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="D132" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F132" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G132" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="133" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="B133" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="D133" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E133" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F133" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G133" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="134" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="B134" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C134" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="D134" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E134" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="F134" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G134" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="135" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="B135" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="C135" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D135" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E135" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F135" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G135" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="136" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="B136" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C136" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="D136" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E136" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F136" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G136" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="137" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="B137" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="C137" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="B107" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C107" s="12" t="s">
+      <c r="D137" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E137" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F137" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G137" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="138" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="D107" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E107" s="12" t="s">
+      <c r="B138" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C138" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="F107" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="G107" s="12" t="s">
+      <c r="D138" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E138" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F138" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G138" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="139" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="B139" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="C139" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="D139" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E139" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F139" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G139" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="140" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="B140" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C140" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="D140" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E140" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F140" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G140" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="141" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="B141" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="C141" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D141" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E141" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F141" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G141" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="142" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="B142" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C142" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="D142" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E142" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F142" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G142" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="143" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="B143" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="C143" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="D143" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E143" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F143" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G143" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="144" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="B144" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C144" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="D144" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E144" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F144" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G144" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="145" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="B145" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="C145" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="D145" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E145" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F145" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G145" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="146" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="B146" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C146" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="D146" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E146" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F146" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G146" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="147" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="B147" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="C147" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="D147" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E147" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F147" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G147" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="148" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="B148" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C148" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="D148" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E148" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F148" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G148" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="149" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="B149" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="C149" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="D149" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E149" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F149" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G149" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C150" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="D150" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E150" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F150" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G150" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="151" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="B151" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="C151" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="D151" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E151" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F151" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G151" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="152" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="B152" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C152" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="D152" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E152" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F152" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G152" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="153" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="B153" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="C153" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="D153" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E153" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F153" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G153" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="154" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="B154" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C154" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="D154" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E154" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F154" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G154" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="155" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="B155" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="C155" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="D155" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E155" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F155" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G155" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="B156" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C156" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="D156" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E156" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F156" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G156" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="157" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B157" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="C157" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="D157" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E157" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F157" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G157" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="158" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="B158" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C158" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="D158" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E158" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F158" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G158" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="159" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="B159" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C159" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D159" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E159" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F159" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G159" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="160" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="B160" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C160" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="D160" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E160" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F160" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G160" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="161" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="B161" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C161" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="D161" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E161" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F161" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G161" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="162" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="B162" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C162" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="D162" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E162" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F162" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G162" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="163" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="B163" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C163" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D163" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E163" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F163" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G163" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="164" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A164" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="B164" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C164" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="D164" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E164" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F164" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G164" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="165" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="B165" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C165" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="D165" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E165" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F165" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G165" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="166" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="B166" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C166" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="D166" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E166" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F166" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G166" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="167" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A167" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B167" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C167" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="D167" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E167" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F167" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G167" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="168" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="B168" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C168" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="D168" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E168" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F168" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G168" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="169" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="B169" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C169" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D169" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E169" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F169" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G169" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="170" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="B170" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C170" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="D170" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E170" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F170" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G170" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="171" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="B171" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C171" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="D171" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E171" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F171" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G171" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="172" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="B172" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C172" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="D172" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E172" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F172" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G172" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="173" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="B173" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C173" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="D173" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E173" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F173" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G173" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="174" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="B174" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C174" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="D174" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E174" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F174" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G174" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="175" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="D175" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E175" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F175" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G175" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="176" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A176" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="B176" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C176" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D176" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E176" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F176" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G176" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="177" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="B177" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D177" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E177" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F177" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G177" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="178" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A178" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="B178" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C178" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="D178" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E178" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F178" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G178" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="179" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A179" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="B179" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C179" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="D179" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E179" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F179" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G179" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="180" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A180" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="B180" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C180" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="D180" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E180" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F180" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G180" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="181" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A181" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="B181" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C181" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="D181" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E181" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F181" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G181" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="182" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="B182" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C182" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="D182" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E182" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F182" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G182" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="183" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A183" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="B183" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="C183" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="D183" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E183" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F183" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G183" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="184" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A184" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B184" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="C184" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="D184" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E184" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F184" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G184" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="185" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A185" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="B185" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="C185" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="D185" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E185" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F185" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G185" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="186" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="B186" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="C186" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="D186" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E186" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F186" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G186" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="187" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A187" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="B187" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="C187" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="D187" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E187" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F187" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G187" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="188" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A188" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="B188" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="C188" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="D188" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E188" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F188" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G188" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="189" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A189" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="B189" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="C189" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="D189" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E189" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F189" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G189" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="190" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="B190" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="C190" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="D190" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E190" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F190" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G190" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="191" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A191" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="B191" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="C191" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="D191" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E191" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F191" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G191" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="192" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A192" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="B192" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="C192" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="D192" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E192" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F192" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G192" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="193" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A193" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="B193" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="C193" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="D193" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E193" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F193" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G193" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="194" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A194" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="B194" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="C194" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="D194" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E194" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F194" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G194" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="195" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A195" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="B195" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="C195" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D195" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E195" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F195" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G195" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="196" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A196" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="B196" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="C196" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="D196" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E196" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F196" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G196" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="197" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A197" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="B197" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="C197" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="D197" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E197" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F197" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G197" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="198" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A198" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="B198" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="C198" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="D198" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E198" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F198" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G198" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="199" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A199" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="B199" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="C199" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="D199" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E199" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F199" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G199" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="200" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A200" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="B200" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="C200" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="D200" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E200" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F200" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G200" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="201" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A201" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="B201" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="C201" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="D201" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E201" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F201" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G201" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="202" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A202" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="B202" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="C202" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="D202" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E202" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F202" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G202" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="203" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A203" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="B203" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="C203" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="D203" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E203" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F203" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G203" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="204" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A204" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="B204" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="C204" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="D204" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E204" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F204" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G204" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="205" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A205" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="B205" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="C205" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="D205" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E205" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F205" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G205" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="206" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A206" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="B206" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="C206" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="D206" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E206" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F206" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G206" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="207" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A207" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="B207" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="C207" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="D207" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E207" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F207" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G207" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="208" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A208" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="B208" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C208" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="D208" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E208" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="F208" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G208" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="209" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A209" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="B209" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="C209" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="D209" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E209" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F209" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G209" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="210" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A210" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="B210" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C210" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="D210" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E210" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="F210" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G210" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="211" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A211" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="B211" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="C211" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="D211" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E211" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F211" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G211" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="212" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A212" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="B212" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C212" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="D212" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E212" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F212" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G212" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="213" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A213" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="B213" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="C213" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="D213" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E213" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F213" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G213" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="214" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A214" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="B214" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C214" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="D214" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E214" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F214" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G214" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="215" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A215" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="B215" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="C215" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="D215" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E215" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F215" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G215" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="216" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A216" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="B216" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C216" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="D216" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E216" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F216" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G216" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="217" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A217" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="B217" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="C217" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="D217" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E217" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F217" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G217" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="218" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A218" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="B218" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C218" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="D218" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E218" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F218" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G218" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="219" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A219" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="B219" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="C219" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="D219" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E219" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F219" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G219" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="220" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A220" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="B220" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C220" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="D220" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E220" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F220" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G220" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="221" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A221" s="12" t="s">
+        <v>485</v>
+      </c>
+      <c r="B221" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="C221" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="D221" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E221" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F221" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G221" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="222" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A222" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="B222" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C222" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="D222" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E222" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F222" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G222" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="223" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A223" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="B223" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="C223" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="D223" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E223" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F223" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G223" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="224" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A224" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="B224" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C224" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="D224" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E224" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F224" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G224" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="225" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A225" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="B225" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="C225" s="12" t="s">
+        <v>494</v>
+      </c>
+      <c r="D225" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E225" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F225" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G225" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="226" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A226" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B226" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C226" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="D226" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E226" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F226" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G226" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="227" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A227" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="B227" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="C227" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="D227" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E227" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F227" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G227" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="228" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A228" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="B228" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C228" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="D228" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E228" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F228" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G228" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="229" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A229" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="B229" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="C229" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="D229" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E229" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F229" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G229" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="230" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="B230" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C230" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="D230" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E230" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F230" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G230" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="231" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A231" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="B231" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="C231" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="D231" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E231" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F231" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G231" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="232" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A232" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="B232" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C232" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="D232" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E232" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F232" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G232" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="233" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A233" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="B233" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="C233" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="D233" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E233" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F233" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G233" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="234" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A234" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="B234" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="C234" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="D234" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E234" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F234" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G234" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="235" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A235" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="B235" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="C235" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="D235" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E235" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="F235" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G235" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="236" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A236" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="B236" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="C236" s="10" t="s">
+        <v>517</v>
+      </c>
+      <c r="D236" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E236" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F236" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G236" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="237" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A237" s="12" t="s">
+        <v>518</v>
+      </c>
+      <c r="B237" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="C237" s="12" t="s">
+        <v>519</v>
+      </c>
+      <c r="D237" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E237" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F237" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G237" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="238" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A238" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="B238" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="C238" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="D238" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E238" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F238" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G238" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="239" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A239" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="B239" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="C239" s="12" t="s">
+        <v>523</v>
+      </c>
+      <c r="D239" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E239" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F239" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G239" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="240" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A240" s="10" t="s">
+        <v>524</v>
+      </c>
+      <c r="B240" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="C240" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="D240" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E240" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F240" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G240" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="241" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A241" s="12" t="s">
+        <v>526</v>
+      </c>
+      <c r="B241" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="C241" s="12" t="s">
+        <v>527</v>
+      </c>
+      <c r="D241" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E241" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F241" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G241" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="242" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A242" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="B242" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="C242" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="D242" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E242" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F242" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G242" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="243" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A243" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="B243" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="C243" s="12" t="s">
+        <v>531</v>
+      </c>
+      <c r="D243" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E243" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="F243" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G243" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="244" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A244" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="B244" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="C244" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="D244" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E244" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F244" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G244" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="245" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A245" s="12" t="s">
+        <v>534</v>
+      </c>
+      <c r="B245" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="C245" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="D245" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E245" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F245" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G245" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="246" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A246" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="B246" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="C246" s="10" t="s">
+        <v>537</v>
+      </c>
+      <c r="D246" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E246" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F246" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G246" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="247" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A247" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="B247" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="C247" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D247" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E247" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F247" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G247" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="248" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A248" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="B248" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="C248" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="D248" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E248" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F248" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G248" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="249" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A249" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="B249" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="C249" s="12" t="s">
+        <v>543</v>
+      </c>
+      <c r="D249" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E249" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F249" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G249" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="250" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A250" s="10" t="s">
+        <v>544</v>
+      </c>
+      <c r="B250" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="C250" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="D250" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E250" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F250" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G250" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="251" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A251" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="B251" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="C251" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="D251" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E251" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F251" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G251" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="252" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A252" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="B252" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="C252" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="D252" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E252" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F252" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G252" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="253" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A253" s="12" t="s">
+        <v>550</v>
+      </c>
+      <c r="B253" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="C253" s="12" t="s">
+        <v>551</v>
+      </c>
+      <c r="D253" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E253" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F253" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G253" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="254" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A254" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="B254" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="C254" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="D254" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E254" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F254" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G254" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="255" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A255" s="12" t="s">
+        <v>554</v>
+      </c>
+      <c r="B255" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="C255" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="D255" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E255" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F255" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G255" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="256" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A256" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="B256" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="C256" s="10" t="s">
+        <v>557</v>
+      </c>
+      <c r="D256" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E256" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F256" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G256" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="257" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A257" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="B257" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="C257" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="D257" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E257" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F257" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G257" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="258" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A258" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="B258" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="C258" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="D258" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E258" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F258" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G258" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="259" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A259" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="B259" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="C259" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="D259" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E259" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="F259" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G259" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="260" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A260" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="B260" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="C260" s="10" t="s">
+        <v>566</v>
+      </c>
+      <c r="D260" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E260" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="F260" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G260" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="261" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A261" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="B261" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="C261" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="D261" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E261" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F261" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G261" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="262" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A262" s="10" t="s">
+        <v>569</v>
+      </c>
+      <c r="B262" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="C262" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="D262" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E262" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F262" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G262" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="263" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A263" s="12" t="s">
+        <v>571</v>
+      </c>
+      <c r="B263" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="C263" s="12" t="s">
+        <v>572</v>
+      </c>
+      <c r="D263" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E263" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F263" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G263" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="264" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A264" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="B264" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="C264" s="10" t="s">
+        <v>574</v>
+      </c>
+      <c r="D264" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E264" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F264" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G264" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="265" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A265" s="12" t="s">
+        <v>575</v>
+      </c>
+      <c r="B265" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="C265" s="12" t="s">
+        <v>576</v>
+      </c>
+      <c r="D265" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E265" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F265" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G265" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="266" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A266" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="B266" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="C266" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="D266" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E266" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F266" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G266" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="267" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A267" s="12" t="s">
+        <v>579</v>
+      </c>
+      <c r="B267" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="C267" s="12" t="s">
+        <v>580</v>
+      </c>
+      <c r="D267" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E267" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F267" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G267" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="268" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A268" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="B268" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="C268" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="D268" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E268" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F268" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G268" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="269" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A269" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="B269" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="C269" s="12" t="s">
+        <v>584</v>
+      </c>
+      <c r="D269" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E269" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F269" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G269" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="270" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A270" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="B270" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="C270" s="10" t="s">
+        <v>586</v>
+      </c>
+      <c r="D270" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E270" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F270" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G270" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="271" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A271" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="B271" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="C271" s="12" t="s">
+        <v>588</v>
+      </c>
+      <c r="D271" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E271" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F271" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G271" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="272" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A272" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="B272" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="C272" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="D272" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E272" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F272" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G272" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="273" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A273" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="B273" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="C273" s="12" t="s">
+        <v>592</v>
+      </c>
+      <c r="D273" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E273" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F273" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G273" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="274" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A274" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="B274" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="C274" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D274" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E274" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F274" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G274" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="275" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A275" s="12" t="s">
+        <v>595</v>
+      </c>
+      <c r="B275" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="C275" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="D275" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E275" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F275" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G275" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="276" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A276" s="10" t="s">
+        <v>597</v>
+      </c>
+      <c r="B276" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="C276" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="D276" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E276" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F276" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G276" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="277" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A277" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="B277" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="C277" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="D277" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E277" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F277" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G277" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="278" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A278" s="10" t="s">
+        <v>601</v>
+      </c>
+      <c r="B278" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="C278" s="10" t="s">
+        <v>602</v>
+      </c>
+      <c r="D278" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E278" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="F278" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G278" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="279" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A279" s="12" t="s">
+        <v>603</v>
+      </c>
+      <c r="B279" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="C279" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="D279" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E279" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F279" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G279" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="280" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A280" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="B280" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="C280" s="10" t="s">
+        <v>606</v>
+      </c>
+      <c r="D280" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E280" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F280" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G280" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="281" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A281" s="12" t="s">
+        <v>607</v>
+      </c>
+      <c r="B281" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="C281" s="12" t="s">
+        <v>608</v>
+      </c>
+      <c r="D281" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E281" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F281" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G281" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="282" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A282" s="10" t="s">
+        <v>609</v>
+      </c>
+      <c r="B282" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="C282" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="D282" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E282" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F282" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G282" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="283" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A283" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="B283" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="C283" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="D283" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E283" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F283" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G283" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="284" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A284" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="B284" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="C284" s="10" t="s">
+        <v>615</v>
+      </c>
+      <c r="D284" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E284" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F284" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G284" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="285" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A285" s="12" t="s">
+        <v>616</v>
+      </c>
+      <c r="B285" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="C285" s="12" t="s">
+        <v>617</v>
+      </c>
+      <c r="D285" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E285" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F285" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G285" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="286" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A286" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="B286" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="C286" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="D286" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E286" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F286" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G286" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="287" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A287" s="12" t="s">
+        <v>620</v>
+      </c>
+      <c r="B287" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="C287" s="12" t="s">
+        <v>621</v>
+      </c>
+      <c r="D287" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E287" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F287" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G287" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="288" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A288" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="B288" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="C288" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="D288" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E288" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="F288" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G288" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="289" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A289" s="12" t="s">
+        <v>624</v>
+      </c>
+      <c r="B289" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="C289" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="D289" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E289" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F289" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G289" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="290" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A290" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="B290" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="C290" s="10" t="s">
+        <v>627</v>
+      </c>
+      <c r="D290" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E290" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F290" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G290" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="291" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A291" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="B291" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="C291" s="12" t="s">
+        <v>629</v>
+      </c>
+      <c r="D291" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E291" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F291" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G291" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="292" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A292" s="10" t="s">
+        <v>630</v>
+      </c>
+      <c r="B292" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="C292" s="10" t="s">
+        <v>631</v>
+      </c>
+      <c r="D292" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E292" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F292" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G292" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="293" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A293" s="12" t="s">
+        <v>632</v>
+      </c>
+      <c r="B293" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="C293" s="12" t="s">
+        <v>633</v>
+      </c>
+      <c r="D293" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E293" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F293" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G293" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="294" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A294" s="10" t="s">
+        <v>634</v>
+      </c>
+      <c r="B294" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="C294" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="D294" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E294" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="F294" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G294" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="295" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A295" s="12" t="s">
+        <v>636</v>
+      </c>
+      <c r="B295" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="C295" s="12" t="s">
+        <v>637</v>
+      </c>
+      <c r="D295" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E295" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F295" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G295" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="296" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A296" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="B296" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="C296" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="D296" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E296" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F296" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G296" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="297" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A297" s="12" t="s">
+        <v>640</v>
+      </c>
+      <c r="B297" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="C297" s="12" t="s">
+        <v>641</v>
+      </c>
+      <c r="D297" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E297" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F297" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G297" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="298" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A298" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="B298" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="C298" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="D298" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E298" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F298" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G298" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="299" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A299" s="12" t="s">
+        <v>644</v>
+      </c>
+      <c r="B299" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="C299" s="12" t="s">
+        <v>645</v>
+      </c>
+      <c r="D299" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E299" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F299" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G299" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="300" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A300" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="B300" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="C300" s="10" t="s">
+        <v>647</v>
+      </c>
+      <c r="D300" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E300" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F300" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G300" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="301" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A301" s="12" t="s">
+        <v>648</v>
+      </c>
+      <c r="B301" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="C301" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="D301" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E301" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F301" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G301" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="302" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A302" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="B302" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="C302" s="10" t="s">
+        <v>651</v>
+      </c>
+      <c r="D302" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E302" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F302" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G302" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="303" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A303" s="12" t="s">
+        <v>652</v>
+      </c>
+      <c r="B303" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="C303" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="D303" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E303" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F303" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G303" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="304" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A304" s="10" t="s">
+        <v>654</v>
+      </c>
+      <c r="B304" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="C304" s="10" t="s">
+        <v>655</v>
+      </c>
+      <c r="D304" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E304" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F304" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G304" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="305" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A305" s="12" t="s">
+        <v>656</v>
+      </c>
+      <c r="B305" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="C305" s="12" t="s">
+        <v>657</v>
+      </c>
+      <c r="D305" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E305" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F305" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G305" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="306" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A306" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="B306" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="C306" s="10" t="s">
+        <v>659</v>
+      </c>
+      <c r="D306" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E306" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F306" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G306" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="307" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A307" s="12" t="s">
+        <v>660</v>
+      </c>
+      <c r="B307" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="C307" s="12" t="s">
+        <v>661</v>
+      </c>
+      <c r="D307" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E307" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F307" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G307" s="12" t="s">
         <v>20</v>
       </c>
     </row>
